--- a/tool/track-aggregator/template/アンケート結果.xlsx
+++ b/tool/track-aggregator/template/アンケート結果.xlsx
@@ -5,28 +5,29 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\businessImprovement\tool\結果集計\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE6CDE2-EAEE-44D9-87B4-67E7F9ACD7F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD81802-C9C6-4099-8525-2667D09211FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="経年比較" sheetId="31" r:id="rId1"/>
     <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId2"/>
     <sheet name="サマリ" sheetId="32" r:id="rId3"/>
-    <sheet name="詳細-ユーザ別" sheetId="30" r:id="rId4"/>
+    <sheet name="サマリ-ユーザー別" sheetId="39" r:id="rId4"/>
     <sheet name="サマリ-会社別" sheetId="34" r:id="rId5"/>
     <sheet name="サマリ-クラス別" sheetId="37" r:id="rId6"/>
     <sheet name="サマリ-ランク別" sheetId="38" r:id="rId7"/>
-    <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId8"/>
+    <sheet name="詳細-ユーザ別" sheetId="30" r:id="rId8"/>
+    <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">サマリ!$B$2:$O$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">経年比較!$B$2:$Q$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'詳細-ユーザ別'!$A$3:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'詳細-ユーザ別'!$A$3:$P$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="211">
   <si>
     <t>目的達成</t>
     <rPh sb="0" eb="2">
@@ -2774,6 +2775,66 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="10" fillId="8" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2783,64 +2844,13 @@
     <xf numFmtId="179" fontId="10" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2860,15 +2870,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -2964,7 +2965,12 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{35DECEAB-A874-4A31-B6F5-75B712B64A43}"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="36">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -3588,11 +3594,11 @@
       </c>
     </row>
     <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="218" t="s">
+      <c r="B2" s="219" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="219"/>
-      <c r="D2" s="224" t="s">
+      <c r="C2" s="220"/>
+      <c r="D2" s="225" t="s">
         <v>54</v>
       </c>
       <c r="E2" s="204" t="s">
@@ -3600,23 +3606,23 @@
       </c>
       <c r="F2" s="205"/>
       <c r="G2" s="206"/>
-      <c r="H2" s="226" t="s">
+      <c r="H2" s="207" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="227"/>
-      <c r="J2" s="227"/>
-      <c r="K2" s="227"/>
-      <c r="L2" s="227"/>
-      <c r="M2" s="227"/>
-      <c r="N2" s="227"/>
-      <c r="O2" s="227"/>
-      <c r="P2" s="227"/>
-      <c r="Q2" s="228"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="208"/>
+      <c r="N2" s="208"/>
+      <c r="O2" s="208"/>
+      <c r="P2" s="208"/>
+      <c r="Q2" s="209"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="220"/>
-      <c r="C3" s="221"/>
-      <c r="D3" s="225"/>
+      <c r="B3" s="221"/>
+      <c r="C3" s="222"/>
+      <c r="D3" s="226"/>
       <c r="E3" s="210" t="s">
         <v>97</v>
       </c>
@@ -3634,9 +3640,9 @@
       <c r="Q3" s="180"/>
     </row>
     <row r="4" spans="1:29" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="222"/>
-      <c r="C4" s="223"/>
-      <c r="D4" s="225"/>
+      <c r="B4" s="223"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="226"/>
       <c r="E4" s="181" t="s">
         <v>141</v>
       </c>
@@ -3864,7 +3870,7 @@
     </row>
     <row r="9" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="214"/>
-      <c r="C9" s="229"/>
+      <c r="C9" s="218"/>
       <c r="D9" s="141" t="s">
         <v>103</v>
       </c>
@@ -4173,11 +4179,11 @@
       <c r="Q15" s="105"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B16" s="218" t="s">
+      <c r="B16" s="219" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="219"/>
-      <c r="D16" s="224" t="s">
+      <c r="C16" s="220"/>
+      <c r="D16" s="225" t="s">
         <v>54</v>
       </c>
       <c r="E16" s="204" t="s">
@@ -4185,23 +4191,23 @@
       </c>
       <c r="F16" s="205"/>
       <c r="G16" s="206"/>
-      <c r="H16" s="207" t="s">
+      <c r="H16" s="227" t="s">
         <v>56</v>
       </c>
-      <c r="I16" s="208"/>
-      <c r="J16" s="208"/>
-      <c r="K16" s="208"/>
-      <c r="L16" s="208"/>
-      <c r="M16" s="208"/>
-      <c r="N16" s="208"/>
-      <c r="O16" s="208"/>
-      <c r="P16" s="208"/>
-      <c r="Q16" s="209"/>
+      <c r="I16" s="228"/>
+      <c r="J16" s="228"/>
+      <c r="K16" s="228"/>
+      <c r="L16" s="228"/>
+      <c r="M16" s="228"/>
+      <c r="N16" s="228"/>
+      <c r="O16" s="228"/>
+      <c r="P16" s="228"/>
+      <c r="Q16" s="229"/>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B17" s="220"/>
-      <c r="C17" s="221"/>
-      <c r="D17" s="225"/>
+      <c r="B17" s="221"/>
+      <c r="C17" s="222"/>
+      <c r="D17" s="226"/>
       <c r="E17" s="210" t="s">
         <v>97</v>
       </c>
@@ -4219,9 +4225,9 @@
       <c r="Q17" s="189"/>
     </row>
     <row r="18" spans="2:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B18" s="222"/>
-      <c r="C18" s="223"/>
-      <c r="D18" s="225"/>
+      <c r="B18" s="223"/>
+      <c r="C18" s="224"/>
+      <c r="D18" s="226"/>
       <c r="E18" s="181" t="s">
         <v>141</v>
       </c>
@@ -4730,11 +4736,11 @@
       <c r="Q28" s="105"/>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="218" t="s">
+      <c r="B29" s="219" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="219"/>
-      <c r="D29" s="224" t="s">
+      <c r="C29" s="220"/>
+      <c r="D29" s="225" t="s">
         <v>54</v>
       </c>
       <c r="E29" s="204" t="s">
@@ -4742,23 +4748,23 @@
       </c>
       <c r="F29" s="205"/>
       <c r="G29" s="206"/>
-      <c r="H29" s="207" t="s">
+      <c r="H29" s="227" t="s">
         <v>56</v>
       </c>
-      <c r="I29" s="208"/>
-      <c r="J29" s="208"/>
-      <c r="K29" s="208"/>
-      <c r="L29" s="208"/>
-      <c r="M29" s="208"/>
-      <c r="N29" s="208"/>
-      <c r="O29" s="208"/>
-      <c r="P29" s="208"/>
-      <c r="Q29" s="209"/>
+      <c r="I29" s="228"/>
+      <c r="J29" s="228"/>
+      <c r="K29" s="228"/>
+      <c r="L29" s="228"/>
+      <c r="M29" s="228"/>
+      <c r="N29" s="228"/>
+      <c r="O29" s="228"/>
+      <c r="P29" s="228"/>
+      <c r="Q29" s="229"/>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="220"/>
-      <c r="C30" s="221"/>
-      <c r="D30" s="225"/>
+      <c r="B30" s="221"/>
+      <c r="C30" s="222"/>
+      <c r="D30" s="226"/>
       <c r="E30" s="210" t="s">
         <v>97</v>
       </c>
@@ -4776,9 +4782,9 @@
       <c r="Q30" s="189"/>
     </row>
     <row r="31" spans="2:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="222"/>
-      <c r="C31" s="223"/>
-      <c r="D31" s="225"/>
+      <c r="B31" s="223"/>
+      <c r="C31" s="224"/>
+      <c r="D31" s="226"/>
       <c r="E31" s="181" t="s">
         <v>141</v>
       </c>
@@ -5692,18 +5698,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:Q2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B5:B14"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="B16:C18"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D16:D18"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="H16:Q16"/>
     <mergeCell ref="E17:G17"/>
@@ -5720,70 +5714,82 @@
     <mergeCell ref="B19:B27"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="B16:C18"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:Q2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B5:B14"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q6">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:Q8">
-    <cfRule type="cellIs" dxfId="33" priority="18" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="34" priority="18" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:Q9">
-    <cfRule type="cellIs" dxfId="32" priority="19" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="33" priority="19" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:Q10">
-    <cfRule type="cellIs" dxfId="31" priority="20" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="32" priority="20" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12:Q13">
-    <cfRule type="cellIs" dxfId="30" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="31" priority="4" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:Q20">
-    <cfRule type="cellIs" dxfId="29" priority="16" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="30" priority="16" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:Q22">
-    <cfRule type="cellIs" dxfId="28" priority="10" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="29" priority="10" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H23:Q23 H39:Q39 H42:Q42">
-    <cfRule type="cellIs" dxfId="27" priority="21" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="28" priority="21" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:Q26">
-    <cfRule type="cellIs" dxfId="26" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="27" priority="9" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:Q33">
-    <cfRule type="cellIs" dxfId="25" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="26" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:Q36">
-    <cfRule type="cellIs" dxfId="24" priority="7" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="25" priority="7" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38:Q38">
-    <cfRule type="cellIs" dxfId="23" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="24" priority="6" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41:Q41">
-    <cfRule type="cellIs" dxfId="22" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5838,10 +5844,10 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="230" t="s">
+      <c r="B2" s="233" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="231"/>
+      <c r="C2" s="234"/>
       <c r="D2" s="242" t="s">
         <v>54</v>
       </c>
@@ -5864,8 +5870,8 @@
       <c r="Q2" s="246"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="232"/>
-      <c r="C3" s="233"/>
+      <c r="B3" s="235"/>
+      <c r="C3" s="236"/>
       <c r="D3" s="243"/>
       <c r="E3" s="247" t="s">
         <v>97</v>
@@ -5884,8 +5890,8 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="234"/>
-      <c r="C4" s="235"/>
+      <c r="B4" s="237"/>
+      <c r="C4" s="238"/>
       <c r="D4" s="243"/>
       <c r="E4" s="85" t="s">
         <v>141</v>
@@ -5931,7 +5937,7 @@
       <c r="B5" s="239" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="236" t="s">
+      <c r="C5" s="230" t="s">
         <v>138</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -5986,7 +5992,7 @@
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B6" s="240"/>
-      <c r="C6" s="237"/>
+      <c r="C6" s="231"/>
       <c r="D6" s="26" t="s">
         <v>103</v>
       </c>
@@ -6040,7 +6046,7 @@
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B7" s="240"/>
-      <c r="C7" s="238"/>
+      <c r="C7" s="232"/>
       <c r="D7" s="83" t="s">
         <v>71</v>
       </c>
@@ -6146,7 +6152,7 @@
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B9" s="240"/>
-      <c r="C9" s="236" t="s">
+      <c r="C9" s="230" t="s">
         <v>102</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -6198,7 +6204,7 @@
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B10" s="240"/>
-      <c r="C10" s="237"/>
+      <c r="C10" s="231"/>
       <c r="D10" s="26" t="s">
         <v>103</v>
       </c>
@@ -6250,7 +6256,7 @@
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="240"/>
-      <c r="C11" s="238"/>
+      <c r="C11" s="232"/>
       <c r="D11" s="34" t="s">
         <v>71</v>
       </c>
@@ -6356,7 +6362,7 @@
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B13" s="240"/>
-      <c r="C13" s="236" t="s">
+      <c r="C13" s="230" t="s">
         <v>143</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -6408,7 +6414,7 @@
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B14" s="240"/>
-      <c r="C14" s="237"/>
+      <c r="C14" s="231"/>
       <c r="D14" s="26" t="s">
         <v>103</v>
       </c>
@@ -6460,7 +6466,7 @@
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B15" s="240"/>
-      <c r="C15" s="238"/>
+      <c r="C15" s="232"/>
       <c r="D15" s="83" t="s">
         <v>71</v>
       </c>
@@ -6577,10 +6583,10 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="230" t="s">
+      <c r="B18" s="233" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="231"/>
+      <c r="C18" s="234"/>
       <c r="D18" s="242" t="s">
         <v>54</v>
       </c>
@@ -6603,8 +6609,8 @@
       <c r="Q18" s="258"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="232"/>
-      <c r="C19" s="233"/>
+      <c r="B19" s="235"/>
+      <c r="C19" s="236"/>
       <c r="D19" s="243"/>
       <c r="E19" s="247" t="s">
         <v>97</v>
@@ -6623,8 +6629,8 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="234"/>
-      <c r="C20" s="235"/>
+      <c r="B20" s="237"/>
+      <c r="C20" s="238"/>
       <c r="D20" s="243"/>
       <c r="E20" s="85" t="s">
         <v>141</v>
@@ -6670,7 +6676,7 @@
       <c r="B21" s="239" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="236" t="s">
+      <c r="C21" s="230" t="s">
         <v>100</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -6731,7 +6737,7 @@
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B22" s="240"/>
-      <c r="C22" s="237"/>
+      <c r="C22" s="231"/>
       <c r="D22" s="26" t="s">
         <v>103</v>
       </c>
@@ -6786,7 +6792,7 @@
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B23" s="240"/>
-      <c r="C23" s="238"/>
+      <c r="C23" s="232"/>
       <c r="D23" s="83" t="s">
         <v>71</v>
       </c>
@@ -6897,7 +6903,7 @@
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B25" s="240"/>
-      <c r="C25" s="236" t="s">
+      <c r="C25" s="230" t="s">
         <v>99</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -6958,7 +6964,7 @@
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B26" s="240"/>
-      <c r="C26" s="237"/>
+      <c r="C26" s="231"/>
       <c r="D26" s="26" t="s">
         <v>103</v>
       </c>
@@ -7013,7 +7019,7 @@
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B27" s="240"/>
-      <c r="C27" s="238"/>
+      <c r="C27" s="232"/>
       <c r="D27" s="83" t="s">
         <v>71</v>
       </c>
@@ -7124,7 +7130,7 @@
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B29" s="240"/>
-      <c r="C29" s="236" t="s">
+      <c r="C29" s="230" t="s">
         <v>98</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -7185,7 +7191,7 @@
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B30" s="240"/>
-      <c r="C30" s="237"/>
+      <c r="C30" s="231"/>
       <c r="D30" s="26" t="s">
         <v>103</v>
       </c>
@@ -7240,7 +7246,7 @@
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B31" s="240"/>
-      <c r="C31" s="238"/>
+      <c r="C31" s="232"/>
       <c r="D31" s="83" t="s">
         <v>71</v>
       </c>
@@ -7362,10 +7368,10 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="230" t="s">
+      <c r="B34" s="233" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="231"/>
+      <c r="C34" s="234"/>
       <c r="D34" s="242" t="s">
         <v>54</v>
       </c>
@@ -7388,8 +7394,8 @@
       <c r="Q34" s="258"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="232"/>
-      <c r="C35" s="233"/>
+      <c r="B35" s="235"/>
+      <c r="C35" s="236"/>
       <c r="D35" s="243"/>
       <c r="E35" s="247" t="s">
         <v>97</v>
@@ -7408,8 +7414,8 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="234"/>
-      <c r="C36" s="235"/>
+      <c r="B36" s="237"/>
+      <c r="C36" s="238"/>
       <c r="D36" s="243"/>
       <c r="E36" s="85" t="s">
         <v>141</v>
@@ -7455,7 +7461,7 @@
       <c r="B37" s="239" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="236" t="s">
+      <c r="C37" s="230" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -7516,7 +7522,7 @@
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B38" s="240"/>
-      <c r="C38" s="237"/>
+      <c r="C38" s="231"/>
       <c r="D38" s="26" t="s">
         <v>103</v>
       </c>
@@ -7571,7 +7577,7 @@
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B39" s="240"/>
-      <c r="C39" s="238"/>
+      <c r="C39" s="232"/>
       <c r="D39" s="83" t="s">
         <v>71</v>
       </c>
@@ -7682,7 +7688,7 @@
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B41" s="240"/>
-      <c r="C41" s="236" t="s">
+      <c r="C41" s="230" t="s">
         <v>80</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -7743,7 +7749,7 @@
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B42" s="240"/>
-      <c r="C42" s="237"/>
+      <c r="C42" s="231"/>
       <c r="D42" s="26" t="s">
         <v>103</v>
       </c>
@@ -7798,7 +7804,7 @@
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B43" s="240"/>
-      <c r="C43" s="238"/>
+      <c r="C43" s="232"/>
       <c r="D43" s="83" t="s">
         <v>71</v>
       </c>
@@ -7909,7 +7915,7 @@
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B45" s="240"/>
-      <c r="C45" s="236" t="s">
+      <c r="C45" s="230" t="s">
         <v>94</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -7970,7 +7976,7 @@
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B46" s="240"/>
-      <c r="C46" s="237"/>
+      <c r="C46" s="231"/>
       <c r="D46" s="26" t="s">
         <v>103</v>
       </c>
@@ -8025,7 +8031,7 @@
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="240"/>
-      <c r="C47" s="238"/>
+      <c r="C47" s="232"/>
       <c r="D47" s="83" t="s">
         <v>71</v>
       </c>
@@ -8136,7 +8142,7 @@
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B49" s="240"/>
-      <c r="C49" s="236" t="s">
+      <c r="C49" s="230" t="s">
         <v>93</v>
       </c>
       <c r="D49" s="33" t="s">
@@ -8188,7 +8194,7 @@
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="240"/>
-      <c r="C50" s="237"/>
+      <c r="C50" s="231"/>
       <c r="D50" s="26" t="s">
         <v>103</v>
       </c>
@@ -8239,7 +8245,7 @@
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B51" s="240"/>
-      <c r="C51" s="238"/>
+      <c r="C51" s="232"/>
       <c r="D51" s="83" t="s">
         <v>71</v>
       </c>
@@ -8741,12 +8747,16 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -8760,90 +8770,86 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">
-    <cfRule type="cellIs" dxfId="21" priority="11" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="22" priority="11" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:Q9">
-    <cfRule type="cellIs" dxfId="20" priority="10" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="21" priority="10" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:Q10">
-    <cfRule type="cellIs" dxfId="19" priority="12" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="12" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:Q11">
-    <cfRule type="cellIs" dxfId="18" priority="14" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="19" priority="14" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:Q13">
-    <cfRule type="cellIs" dxfId="17" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="9" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:Q14 H22:Q22 H26:Q26 H30:Q30 H38:Q38 H42:Q42 H46:Q46 H50:Q50">
-    <cfRule type="cellIs" dxfId="16" priority="16" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:Q15 H23:Q23 H31:Q31 H39:Q39 H43:Q43">
-    <cfRule type="cellIs" dxfId="15" priority="18" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="16" priority="18" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:Q21">
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="15" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:Q25">
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:Q27 H47:Q47 H51:Q51">
-    <cfRule type="cellIs" dxfId="12" priority="15" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="13" priority="15" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29:Q29">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37:Q37">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41:Q41">
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45:Q45">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H49:Q49">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9017,7 +9023,7 @@
       <c r="O6" s="114"/>
     </row>
     <row r="7" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="229"/>
+      <c r="B7" s="218"/>
       <c r="C7" s="115"/>
       <c r="D7" s="115"/>
       <c r="E7" s="116"/>
@@ -9102,22 +9108,22 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="C5:E5">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:O6">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:O7">
-    <cfRule type="cellIs" dxfId="4" priority="13" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="13" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:O8">
-    <cfRule type="cellIs" dxfId="3" priority="14" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="14" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9152,6 +9158,484 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86286144-F6F8-4142-BAA1-C8861DBF28F2}">
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="19.296875" style="100" customWidth="1"/>
+    <col min="2" max="2" width="30.69921875" style="100" customWidth="1"/>
+    <col min="3" max="3" width="40.69921875" style="100" customWidth="1"/>
+    <col min="4" max="5" width="15.69921875" style="100" customWidth="1"/>
+    <col min="6" max="15" width="14.69921875" style="96" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A1" s="94" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="95"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="F3" s="197" t="s">
+        <v>206</v>
+      </c>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
+      <c r="L3" s="198"/>
+      <c r="M3" s="198"/>
+      <c r="N3" s="198"/>
+      <c r="O3" s="199"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A4" s="93" t="s">
+        <v>157</v>
+      </c>
+      <c r="B4" s="93" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="93" t="s">
+        <v>158</v>
+      </c>
+      <c r="D4" s="93" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="93" t="s">
+        <v>160</v>
+      </c>
+      <c r="F4" s="97" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="97" t="s">
+        <v>164</v>
+      </c>
+      <c r="H4" s="97" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="97" t="s">
+        <v>166</v>
+      </c>
+      <c r="J4" s="97" t="s">
+        <v>167</v>
+      </c>
+      <c r="K4" s="97" t="s">
+        <v>168</v>
+      </c>
+      <c r="L4" s="97" t="s">
+        <v>169</v>
+      </c>
+      <c r="M4" s="97" t="s">
+        <v>170</v>
+      </c>
+      <c r="N4" s="97" t="s">
+        <v>171</v>
+      </c>
+      <c r="O4" s="97" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A5" s="98" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="203"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="203"/>
+      <c r="I5" s="203"/>
+      <c r="J5" s="203"/>
+      <c r="K5" s="203"/>
+      <c r="L5" s="203"/>
+      <c r="M5" s="203"/>
+      <c r="N5" s="203"/>
+      <c r="O5" s="203"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="F5:O5">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThanOrEqual">
+      <formula>3.4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D283FD5-20E4-4A5F-8CE0-6E0AB2CC1AD7}">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="40.69921875" style="195" customWidth="1"/>
+    <col min="2" max="13" width="14.69921875" style="96" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A1" s="94" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A2" s="94"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A3" s="196"/>
+      <c r="B3" s="197" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
+      <c r="L3" s="198"/>
+      <c r="M3" s="199"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A4" s="93" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" s="201" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="201" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="97" t="s">
+        <v>163</v>
+      </c>
+      <c r="E4" s="97" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" s="97" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4" s="97" t="s">
+        <v>166</v>
+      </c>
+      <c r="H4" s="97" t="s">
+        <v>167</v>
+      </c>
+      <c r="I4" s="97" t="s">
+        <v>168</v>
+      </c>
+      <c r="J4" s="97" t="s">
+        <v>169</v>
+      </c>
+      <c r="K4" s="97" t="s">
+        <v>170</v>
+      </c>
+      <c r="L4" s="97" t="s">
+        <v>171</v>
+      </c>
+      <c r="M4" s="97" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A5" s="200" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" s="202"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="203"/>
+      <c r="F5" s="203"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="203"/>
+      <c r="I5" s="203"/>
+      <c r="J5" s="203"/>
+      <c r="K5" s="203"/>
+      <c r="L5" s="203"/>
+      <c r="M5" s="203"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="D5:M5">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
+      <formula>3.4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20657923-2F38-4DA8-AAA7-2504A3495A9C}">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="40.69921875" style="195" customWidth="1"/>
+    <col min="2" max="13" width="14.69921875" style="96" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A1" s="94" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A2" s="94"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A3" s="196"/>
+      <c r="B3" s="197" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
+      <c r="L3" s="198"/>
+      <c r="M3" s="199"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A4" s="93" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="201" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="201" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="97" t="s">
+        <v>163</v>
+      </c>
+      <c r="E4" s="97" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" s="97" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4" s="97" t="s">
+        <v>166</v>
+      </c>
+      <c r="H4" s="97" t="s">
+        <v>167</v>
+      </c>
+      <c r="I4" s="97" t="s">
+        <v>168</v>
+      </c>
+      <c r="J4" s="97" t="s">
+        <v>169</v>
+      </c>
+      <c r="K4" s="97" t="s">
+        <v>170</v>
+      </c>
+      <c r="L4" s="97" t="s">
+        <v>171</v>
+      </c>
+      <c r="M4" s="97" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A5" s="200" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" s="202"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="203"/>
+      <c r="F5" s="203"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="203"/>
+      <c r="I5" s="203"/>
+      <c r="J5" s="203"/>
+      <c r="K5" s="203"/>
+      <c r="L5" s="203"/>
+      <c r="M5" s="203"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="D5:M5">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThanOrEqual">
+      <formula>3.4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A3F122-A8D4-4240-B606-D85C64EBC3DE}">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="40.69921875" style="195" customWidth="1"/>
+    <col min="2" max="13" width="14.69921875" style="96" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A1" s="94" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A2" s="94"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A3" s="196"/>
+      <c r="B3" s="197" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
+      <c r="L3" s="198"/>
+      <c r="M3" s="199"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A4" s="93" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="201" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="201" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="97" t="s">
+        <v>163</v>
+      </c>
+      <c r="E4" s="97" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" s="97" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4" s="97" t="s">
+        <v>166</v>
+      </c>
+      <c r="H4" s="97" t="s">
+        <v>167</v>
+      </c>
+      <c r="I4" s="97" t="s">
+        <v>168</v>
+      </c>
+      <c r="J4" s="97" t="s">
+        <v>169</v>
+      </c>
+      <c r="K4" s="97" t="s">
+        <v>170</v>
+      </c>
+      <c r="L4" s="97" t="s">
+        <v>171</v>
+      </c>
+      <c r="M4" s="97" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A5" s="200" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" s="202"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="203"/>
+      <c r="F5" s="203"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="203"/>
+      <c r="I5" s="203"/>
+      <c r="J5" s="203"/>
+      <c r="K5" s="203"/>
+      <c r="L5" s="203"/>
+      <c r="M5" s="203"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="D5:M5">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
+      <formula>3.4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{641A4A2E-373C-41E1-A3D4-3CA1E92913A7}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
@@ -9412,355 +9896,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D283FD5-20E4-4A5F-8CE0-6E0AB2CC1AD7}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="40.69921875" style="195" customWidth="1"/>
-    <col min="2" max="13" width="14.69921875" style="96" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A1" s="94" t="s">
-        <v>204</v>
-      </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" s="94"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="196"/>
-      <c r="B3" s="197" t="s">
-        <v>206</v>
-      </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
-      <c r="L3" s="198"/>
-      <c r="M3" s="199"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A4" s="93" t="s">
-        <v>205</v>
-      </c>
-      <c r="B4" s="201" t="s">
-        <v>209</v>
-      </c>
-      <c r="C4" s="201" t="s">
-        <v>210</v>
-      </c>
-      <c r="D4" s="97" t="s">
-        <v>163</v>
-      </c>
-      <c r="E4" s="97" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" s="97" t="s">
-        <v>165</v>
-      </c>
-      <c r="G4" s="97" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" s="97" t="s">
-        <v>167</v>
-      </c>
-      <c r="I4" s="97" t="s">
-        <v>168</v>
-      </c>
-      <c r="J4" s="97" t="s">
-        <v>169</v>
-      </c>
-      <c r="K4" s="97" t="s">
-        <v>170</v>
-      </c>
-      <c r="L4" s="97" t="s">
-        <v>171</v>
-      </c>
-      <c r="M4" s="97" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="200" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="202"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="203"/>
-      <c r="E5" s="203"/>
-      <c r="F5" s="203"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="203"/>
-      <c r="I5" s="203"/>
-      <c r="J5" s="203"/>
-      <c r="K5" s="203"/>
-      <c r="L5" s="203"/>
-      <c r="M5" s="203"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="D5:M5">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20657923-2F38-4DA8-AAA7-2504A3495A9C}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="40.69921875" style="195" customWidth="1"/>
-    <col min="2" max="13" width="14.69921875" style="96" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A1" s="94" t="s">
-        <v>207</v>
-      </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" s="94"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="196"/>
-      <c r="B3" s="197" t="s">
-        <v>206</v>
-      </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
-      <c r="L3" s="198"/>
-      <c r="M3" s="199"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A4" s="93" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" s="201" t="s">
-        <v>209</v>
-      </c>
-      <c r="C4" s="201" t="s">
-        <v>210</v>
-      </c>
-      <c r="D4" s="97" t="s">
-        <v>163</v>
-      </c>
-      <c r="E4" s="97" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" s="97" t="s">
-        <v>165</v>
-      </c>
-      <c r="G4" s="97" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" s="97" t="s">
-        <v>167</v>
-      </c>
-      <c r="I4" s="97" t="s">
-        <v>168</v>
-      </c>
-      <c r="J4" s="97" t="s">
-        <v>169</v>
-      </c>
-      <c r="K4" s="97" t="s">
-        <v>170</v>
-      </c>
-      <c r="L4" s="97" t="s">
-        <v>171</v>
-      </c>
-      <c r="M4" s="97" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="200" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="202"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="203"/>
-      <c r="E5" s="203"/>
-      <c r="F5" s="203"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="203"/>
-      <c r="I5" s="203"/>
-      <c r="J5" s="203"/>
-      <c r="K5" s="203"/>
-      <c r="L5" s="203"/>
-      <c r="M5" s="203"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="D5:M5">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A3F122-A8D4-4240-B606-D85C64EBC3DE}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="40.69921875" style="195" customWidth="1"/>
-    <col min="2" max="13" width="14.69921875" style="96" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A1" s="94" t="s">
-        <v>208</v>
-      </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" s="94"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="196"/>
-      <c r="B3" s="197" t="s">
-        <v>206</v>
-      </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
-      <c r="L3" s="198"/>
-      <c r="M3" s="199"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A4" s="93" t="s">
-        <v>160</v>
-      </c>
-      <c r="B4" s="201" t="s">
-        <v>209</v>
-      </c>
-      <c r="C4" s="201" t="s">
-        <v>210</v>
-      </c>
-      <c r="D4" s="97" t="s">
-        <v>163</v>
-      </c>
-      <c r="E4" s="97" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" s="97" t="s">
-        <v>165</v>
-      </c>
-      <c r="G4" s="97" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" s="97" t="s">
-        <v>167</v>
-      </c>
-      <c r="I4" s="97" t="s">
-        <v>168</v>
-      </c>
-      <c r="J4" s="97" t="s">
-        <v>169</v>
-      </c>
-      <c r="K4" s="97" t="s">
-        <v>170</v>
-      </c>
-      <c r="L4" s="97" t="s">
-        <v>171</v>
-      </c>
-      <c r="M4" s="97" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="200" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="202"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="203"/>
-      <c r="E5" s="203"/>
-      <c r="F5" s="203"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="203"/>
-      <c r="I5" s="203"/>
-      <c r="J5" s="203"/>
-      <c r="K5" s="203"/>
-      <c r="L5" s="203"/>
-      <c r="M5" s="203"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="D5:M5">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>

--- a/tool/track-aggregator/template/アンケート結果.xlsx
+++ b/tool/track-aggregator/template/アンケート結果.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD81802-C9C6-4099-8525-2667D09211FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1C7AC3-17F6-4FA3-A7CF-E8991EF34B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="経年比較" sheetId="31" r:id="rId1"/>
@@ -2775,6 +2775,63 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="10" fillId="8" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="8" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2784,64 +2841,25 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2852,24 +2870,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -3594,11 +3594,11 @@
       </c>
     </row>
     <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="219" t="s">
+      <c r="B2" s="218" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="220"/>
-      <c r="D2" s="225" t="s">
+      <c r="C2" s="219"/>
+      <c r="D2" s="224" t="s">
         <v>54</v>
       </c>
       <c r="E2" s="204" t="s">
@@ -3606,23 +3606,23 @@
       </c>
       <c r="F2" s="205"/>
       <c r="G2" s="206"/>
-      <c r="H2" s="207" t="s">
+      <c r="H2" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
-      <c r="M2" s="208"/>
-      <c r="N2" s="208"/>
-      <c r="O2" s="208"/>
-      <c r="P2" s="208"/>
-      <c r="Q2" s="209"/>
+      <c r="I2" s="227"/>
+      <c r="J2" s="227"/>
+      <c r="K2" s="227"/>
+      <c r="L2" s="227"/>
+      <c r="M2" s="227"/>
+      <c r="N2" s="227"/>
+      <c r="O2" s="227"/>
+      <c r="P2" s="227"/>
+      <c r="Q2" s="228"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="221"/>
-      <c r="C3" s="222"/>
-      <c r="D3" s="226"/>
+      <c r="B3" s="220"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="225"/>
       <c r="E3" s="210" t="s">
         <v>97</v>
       </c>
@@ -3640,9 +3640,9 @@
       <c r="Q3" s="180"/>
     </row>
     <row r="4" spans="1:29" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="223"/>
-      <c r="C4" s="224"/>
-      <c r="D4" s="226"/>
+      <c r="B4" s="222"/>
+      <c r="C4" s="223"/>
+      <c r="D4" s="225"/>
       <c r="E4" s="181" t="s">
         <v>141</v>
       </c>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="9" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="214"/>
-      <c r="C9" s="218"/>
+      <c r="C9" s="229"/>
       <c r="D9" s="141" t="s">
         <v>103</v>
       </c>
@@ -4179,11 +4179,11 @@
       <c r="Q15" s="105"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B16" s="219" t="s">
+      <c r="B16" s="218" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="220"/>
-      <c r="D16" s="225" t="s">
+      <c r="C16" s="219"/>
+      <c r="D16" s="224" t="s">
         <v>54</v>
       </c>
       <c r="E16" s="204" t="s">
@@ -4191,23 +4191,23 @@
       </c>
       <c r="F16" s="205"/>
       <c r="G16" s="206"/>
-      <c r="H16" s="227" t="s">
+      <c r="H16" s="207" t="s">
         <v>56</v>
       </c>
-      <c r="I16" s="228"/>
-      <c r="J16" s="228"/>
-      <c r="K16" s="228"/>
-      <c r="L16" s="228"/>
-      <c r="M16" s="228"/>
-      <c r="N16" s="228"/>
-      <c r="O16" s="228"/>
-      <c r="P16" s="228"/>
-      <c r="Q16" s="229"/>
+      <c r="I16" s="208"/>
+      <c r="J16" s="208"/>
+      <c r="K16" s="208"/>
+      <c r="L16" s="208"/>
+      <c r="M16" s="208"/>
+      <c r="N16" s="208"/>
+      <c r="O16" s="208"/>
+      <c r="P16" s="208"/>
+      <c r="Q16" s="209"/>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B17" s="221"/>
-      <c r="C17" s="222"/>
-      <c r="D17" s="226"/>
+      <c r="B17" s="220"/>
+      <c r="C17" s="221"/>
+      <c r="D17" s="225"/>
       <c r="E17" s="210" t="s">
         <v>97</v>
       </c>
@@ -4225,9 +4225,9 @@
       <c r="Q17" s="189"/>
     </row>
     <row r="18" spans="2:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B18" s="223"/>
-      <c r="C18" s="224"/>
-      <c r="D18" s="226"/>
+      <c r="B18" s="222"/>
+      <c r="C18" s="223"/>
+      <c r="D18" s="225"/>
       <c r="E18" s="181" t="s">
         <v>141</v>
       </c>
@@ -4736,11 +4736,11 @@
       <c r="Q28" s="105"/>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="219" t="s">
+      <c r="B29" s="218" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="220"/>
-      <c r="D29" s="225" t="s">
+      <c r="C29" s="219"/>
+      <c r="D29" s="224" t="s">
         <v>54</v>
       </c>
       <c r="E29" s="204" t="s">
@@ -4748,23 +4748,23 @@
       </c>
       <c r="F29" s="205"/>
       <c r="G29" s="206"/>
-      <c r="H29" s="227" t="s">
+      <c r="H29" s="207" t="s">
         <v>56</v>
       </c>
-      <c r="I29" s="228"/>
-      <c r="J29" s="228"/>
-      <c r="K29" s="228"/>
-      <c r="L29" s="228"/>
-      <c r="M29" s="228"/>
-      <c r="N29" s="228"/>
-      <c r="O29" s="228"/>
-      <c r="P29" s="228"/>
-      <c r="Q29" s="229"/>
+      <c r="I29" s="208"/>
+      <c r="J29" s="208"/>
+      <c r="K29" s="208"/>
+      <c r="L29" s="208"/>
+      <c r="M29" s="208"/>
+      <c r="N29" s="208"/>
+      <c r="O29" s="208"/>
+      <c r="P29" s="208"/>
+      <c r="Q29" s="209"/>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="221"/>
-      <c r="C30" s="222"/>
-      <c r="D30" s="226"/>
+      <c r="B30" s="220"/>
+      <c r="C30" s="221"/>
+      <c r="D30" s="225"/>
       <c r="E30" s="210" t="s">
         <v>97</v>
       </c>
@@ -4782,9 +4782,9 @@
       <c r="Q30" s="189"/>
     </row>
     <row r="31" spans="2:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="223"/>
-      <c r="C31" s="224"/>
-      <c r="D31" s="226"/>
+      <c r="B31" s="222"/>
+      <c r="C31" s="223"/>
+      <c r="D31" s="225"/>
       <c r="E31" s="181" t="s">
         <v>141</v>
       </c>
@@ -5698,6 +5698,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:Q2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B5:B14"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="B16:C18"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D16:D18"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="H16:Q16"/>
     <mergeCell ref="E17:G17"/>
@@ -5714,18 +5726,6 @@
     <mergeCell ref="B19:B27"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="B16:C18"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:Q2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B5:B14"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C12:C13"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q6">
@@ -5844,10 +5844,10 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="233" t="s">
+      <c r="B2" s="230" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="234"/>
+      <c r="C2" s="231"/>
       <c r="D2" s="242" t="s">
         <v>54</v>
       </c>
@@ -5870,8 +5870,8 @@
       <c r="Q2" s="246"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="235"/>
-      <c r="C3" s="236"/>
+      <c r="B3" s="232"/>
+      <c r="C3" s="233"/>
       <c r="D3" s="243"/>
       <c r="E3" s="247" t="s">
         <v>97</v>
@@ -5890,8 +5890,8 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="237"/>
-      <c r="C4" s="238"/>
+      <c r="B4" s="234"/>
+      <c r="C4" s="235"/>
       <c r="D4" s="243"/>
       <c r="E4" s="85" t="s">
         <v>141</v>
@@ -5937,7 +5937,7 @@
       <c r="B5" s="239" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="230" t="s">
+      <c r="C5" s="236" t="s">
         <v>138</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -5992,7 +5992,7 @@
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B6" s="240"/>
-      <c r="C6" s="231"/>
+      <c r="C6" s="237"/>
       <c r="D6" s="26" t="s">
         <v>103</v>
       </c>
@@ -6046,7 +6046,7 @@
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B7" s="240"/>
-      <c r="C7" s="232"/>
+      <c r="C7" s="238"/>
       <c r="D7" s="83" t="s">
         <v>71</v>
       </c>
@@ -6152,7 +6152,7 @@
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B9" s="240"/>
-      <c r="C9" s="230" t="s">
+      <c r="C9" s="236" t="s">
         <v>102</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -6204,7 +6204,7 @@
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B10" s="240"/>
-      <c r="C10" s="231"/>
+      <c r="C10" s="237"/>
       <c r="D10" s="26" t="s">
         <v>103</v>
       </c>
@@ -6256,7 +6256,7 @@
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="240"/>
-      <c r="C11" s="232"/>
+      <c r="C11" s="238"/>
       <c r="D11" s="34" t="s">
         <v>71</v>
       </c>
@@ -6362,7 +6362,7 @@
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B13" s="240"/>
-      <c r="C13" s="230" t="s">
+      <c r="C13" s="236" t="s">
         <v>143</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -6414,7 +6414,7 @@
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B14" s="240"/>
-      <c r="C14" s="231"/>
+      <c r="C14" s="237"/>
       <c r="D14" s="26" t="s">
         <v>103</v>
       </c>
@@ -6466,7 +6466,7 @@
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B15" s="240"/>
-      <c r="C15" s="232"/>
+      <c r="C15" s="238"/>
       <c r="D15" s="83" t="s">
         <v>71</v>
       </c>
@@ -6583,10 +6583,10 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="233" t="s">
+      <c r="B18" s="230" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="234"/>
+      <c r="C18" s="231"/>
       <c r="D18" s="242" t="s">
         <v>54</v>
       </c>
@@ -6609,8 +6609,8 @@
       <c r="Q18" s="258"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="235"/>
-      <c r="C19" s="236"/>
+      <c r="B19" s="232"/>
+      <c r="C19" s="233"/>
       <c r="D19" s="243"/>
       <c r="E19" s="247" t="s">
         <v>97</v>
@@ -6629,8 +6629,8 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="237"/>
-      <c r="C20" s="238"/>
+      <c r="B20" s="234"/>
+      <c r="C20" s="235"/>
       <c r="D20" s="243"/>
       <c r="E20" s="85" t="s">
         <v>141</v>
@@ -6676,7 +6676,7 @@
       <c r="B21" s="239" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="230" t="s">
+      <c r="C21" s="236" t="s">
         <v>100</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -6737,7 +6737,7 @@
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B22" s="240"/>
-      <c r="C22" s="231"/>
+      <c r="C22" s="237"/>
       <c r="D22" s="26" t="s">
         <v>103</v>
       </c>
@@ -6792,7 +6792,7 @@
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B23" s="240"/>
-      <c r="C23" s="232"/>
+      <c r="C23" s="238"/>
       <c r="D23" s="83" t="s">
         <v>71</v>
       </c>
@@ -6903,7 +6903,7 @@
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B25" s="240"/>
-      <c r="C25" s="230" t="s">
+      <c r="C25" s="236" t="s">
         <v>99</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -6964,7 +6964,7 @@
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B26" s="240"/>
-      <c r="C26" s="231"/>
+      <c r="C26" s="237"/>
       <c r="D26" s="26" t="s">
         <v>103</v>
       </c>
@@ -7019,7 +7019,7 @@
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B27" s="240"/>
-      <c r="C27" s="232"/>
+      <c r="C27" s="238"/>
       <c r="D27" s="83" t="s">
         <v>71</v>
       </c>
@@ -7130,7 +7130,7 @@
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B29" s="240"/>
-      <c r="C29" s="230" t="s">
+      <c r="C29" s="236" t="s">
         <v>98</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -7191,7 +7191,7 @@
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B30" s="240"/>
-      <c r="C30" s="231"/>
+      <c r="C30" s="237"/>
       <c r="D30" s="26" t="s">
         <v>103</v>
       </c>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B31" s="240"/>
-      <c r="C31" s="232"/>
+      <c r="C31" s="238"/>
       <c r="D31" s="83" t="s">
         <v>71</v>
       </c>
@@ -7368,10 +7368,10 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="233" t="s">
+      <c r="B34" s="230" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="234"/>
+      <c r="C34" s="231"/>
       <c r="D34" s="242" t="s">
         <v>54</v>
       </c>
@@ -7394,8 +7394,8 @@
       <c r="Q34" s="258"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="235"/>
-      <c r="C35" s="236"/>
+      <c r="B35" s="232"/>
+      <c r="C35" s="233"/>
       <c r="D35" s="243"/>
       <c r="E35" s="247" t="s">
         <v>97</v>
@@ -7414,8 +7414,8 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="237"/>
-      <c r="C36" s="238"/>
+      <c r="B36" s="234"/>
+      <c r="C36" s="235"/>
       <c r="D36" s="243"/>
       <c r="E36" s="85" t="s">
         <v>141</v>
@@ -7461,7 +7461,7 @@
       <c r="B37" s="239" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="230" t="s">
+      <c r="C37" s="236" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -7522,7 +7522,7 @@
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B38" s="240"/>
-      <c r="C38" s="231"/>
+      <c r="C38" s="237"/>
       <c r="D38" s="26" t="s">
         <v>103</v>
       </c>
@@ -7577,7 +7577,7 @@
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B39" s="240"/>
-      <c r="C39" s="232"/>
+      <c r="C39" s="238"/>
       <c r="D39" s="83" t="s">
         <v>71</v>
       </c>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B41" s="240"/>
-      <c r="C41" s="230" t="s">
+      <c r="C41" s="236" t="s">
         <v>80</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -7749,7 +7749,7 @@
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B42" s="240"/>
-      <c r="C42" s="231"/>
+      <c r="C42" s="237"/>
       <c r="D42" s="26" t="s">
         <v>103</v>
       </c>
@@ -7804,7 +7804,7 @@
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B43" s="240"/>
-      <c r="C43" s="232"/>
+      <c r="C43" s="238"/>
       <c r="D43" s="83" t="s">
         <v>71</v>
       </c>
@@ -7915,7 +7915,7 @@
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B45" s="240"/>
-      <c r="C45" s="230" t="s">
+      <c r="C45" s="236" t="s">
         <v>94</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -7976,7 +7976,7 @@
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B46" s="240"/>
-      <c r="C46" s="231"/>
+      <c r="C46" s="237"/>
       <c r="D46" s="26" t="s">
         <v>103</v>
       </c>
@@ -8031,7 +8031,7 @@
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="240"/>
-      <c r="C47" s="232"/>
+      <c r="C47" s="238"/>
       <c r="D47" s="83" t="s">
         <v>71</v>
       </c>
@@ -8142,7 +8142,7 @@
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B49" s="240"/>
-      <c r="C49" s="230" t="s">
+      <c r="C49" s="236" t="s">
         <v>93</v>
       </c>
       <c r="D49" s="33" t="s">
@@ -8194,7 +8194,7 @@
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="240"/>
-      <c r="C50" s="231"/>
+      <c r="C50" s="237"/>
       <c r="D50" s="26" t="s">
         <v>103</v>
       </c>
@@ -8245,7 +8245,7 @@
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B51" s="240"/>
-      <c r="C51" s="232"/>
+      <c r="C51" s="238"/>
       <c r="D51" s="83" t="s">
         <v>71</v>
       </c>
@@ -8747,16 +8747,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -8770,12 +8766,16 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">
@@ -9023,7 +9023,7 @@
       <c r="O6" s="114"/>
     </row>
     <row r="7" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="218"/>
+      <c r="B7" s="229"/>
       <c r="C7" s="115"/>
       <c r="D7" s="115"/>
       <c r="E7" s="116"/>

--- a/tool/track-aggregator/template/アンケート結果.xlsx
+++ b/tool/track-aggregator/template/アンケート結果.xlsx
@@ -8,26 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1C7AC3-17F6-4FA3-A7CF-E8991EF34B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4871105E-0667-4D55-937D-CA93A376B4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="経年比較" sheetId="31" r:id="rId1"/>
-    <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId2"/>
-    <sheet name="サマリ" sheetId="32" r:id="rId3"/>
-    <sheet name="サマリ-ユーザー別" sheetId="39" r:id="rId4"/>
-    <sheet name="サマリ-会社別" sheetId="34" r:id="rId5"/>
-    <sheet name="サマリ-クラス別" sheetId="37" r:id="rId6"/>
-    <sheet name="サマリ-ランク別" sheetId="38" r:id="rId7"/>
-    <sheet name="詳細-ユーザ別" sheetId="30" r:id="rId8"/>
-    <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId9"/>
+    <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId1"/>
+    <sheet name="サマリ-ユーザー別" sheetId="39" r:id="rId2"/>
+    <sheet name="サマリ-会社別" sheetId="34" r:id="rId3"/>
+    <sheet name="サマリ-クラス別" sheetId="37" r:id="rId4"/>
+    <sheet name="サマリ-ランク別" sheetId="38" r:id="rId5"/>
+    <sheet name="詳細-ユーザ別" sheetId="30" r:id="rId6"/>
+    <sheet name="ビジネス基礎（Day5)" sheetId="13" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">サマリ!$B$2:$O$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">経年比較!$B$2:$Q$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'詳細-ユーザ別'!$A$3:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'詳細-ユーザ別'!$A$3:$P$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="203">
   <si>
     <t>目的達成</t>
     <rPh sb="0" eb="2">
@@ -391,10 +387,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>-</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>不合格</t>
     <rPh sb="0" eb="3">
       <t>フゴウカク</t>
@@ -866,16 +858,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社会を支えるITサービス</t>
-    <rPh sb="0" eb="2">
-      <t>シャカイ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ササ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>中央値</t>
     <rPh sb="0" eb="3">
       <t>チュウオウチ</t>
@@ -887,40 +869,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>FY2026</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>{結果データ}</t>
     <rPh sb="1" eb="3">
       <t>ケッカ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>データベース技術入門</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Web技術入門</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>システム開発演習</t>
-    <rPh sb="4" eb="6">
-      <t>カイハツ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>エンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>研修コース名</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1300,7 +1252,7 @@
     <numFmt numFmtId="178" formatCode="0.00_ "/>
     <numFmt numFmtId="179" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1391,21 +1343,6 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1475,7 +1412,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -1980,141 +1917,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -2153,7 +1955,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="268">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2448,10 +2250,10 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2466,279 +2268,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="9" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="46" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="5" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="5" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="6" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="6" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="6" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="43" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="6" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="6" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="6" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="9" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="9" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2751,7 +2280,7 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2766,82 +2295,13 @@
     <xf numFmtId="179" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2862,15 +2322,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2929,33 +2380,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="5" fillId="8" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="47" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="49" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2965,7 +2389,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{35DECEAB-A874-4A31-B6F5-75B712B64A43}"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="19">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -2985,38 +2409,6 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3114,133 +2506,6 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3570,2260 +2835,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738A7942-48C0-418C-A267-8ECE9048A1F1}">
-  <sheetPr>
-    <tabColor theme="7" tint="0.39997558519241921"/>
-  </sheetPr>
-  <dimension ref="A1:AC65"/>
-  <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="2.59765625" style="104" customWidth="1"/>
-    <col min="2" max="2" width="2.796875" style="104" customWidth="1"/>
-    <col min="3" max="3" width="25.19921875" style="104" customWidth="1"/>
-    <col min="4" max="4" width="10.296875" style="104" customWidth="1"/>
-    <col min="5" max="6" width="10.69921875" style="105" customWidth="1"/>
-    <col min="7" max="7" width="10.69921875" style="104" customWidth="1"/>
-    <col min="8" max="8" width="14.19921875" style="104" bestFit="1" customWidth="1"/>
-    <col min="9" max="17" width="9.5" style="104" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.19921875" style="104"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="104" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="218" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="219"/>
-      <c r="D2" s="224" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="204" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="205"/>
-      <c r="G2" s="206"/>
-      <c r="H2" s="226" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="227"/>
-      <c r="J2" s="227"/>
-      <c r="K2" s="227"/>
-      <c r="L2" s="227"/>
-      <c r="M2" s="227"/>
-      <c r="N2" s="227"/>
-      <c r="O2" s="227"/>
-      <c r="P2" s="227"/>
-      <c r="Q2" s="228"/>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="220"/>
-      <c r="C3" s="221"/>
-      <c r="D3" s="225"/>
-      <c r="E3" s="210" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="211"/>
-      <c r="G3" s="212"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="179"/>
-      <c r="J3" s="179"/>
-      <c r="K3" s="179"/>
-      <c r="L3" s="179"/>
-      <c r="M3" s="179"/>
-      <c r="N3" s="179"/>
-      <c r="O3" s="179"/>
-      <c r="P3" s="179"/>
-      <c r="Q3" s="180"/>
-    </row>
-    <row r="4" spans="1:29" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="222"/>
-      <c r="C4" s="223"/>
-      <c r="D4" s="225"/>
-      <c r="E4" s="181" t="s">
-        <v>141</v>
-      </c>
-      <c r="F4" s="182" t="s">
-        <v>149</v>
-      </c>
-      <c r="G4" s="183" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="184" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="185" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" s="185" t="s">
-        <v>60</v>
-      </c>
-      <c r="K4" s="185" t="s">
-        <v>140</v>
-      </c>
-      <c r="L4" s="185" t="s">
-        <v>61</v>
-      </c>
-      <c r="M4" s="185" t="s">
-        <v>62</v>
-      </c>
-      <c r="N4" s="185" t="s">
-        <v>63</v>
-      </c>
-      <c r="O4" s="185" t="s">
-        <v>64</v>
-      </c>
-      <c r="P4" s="185" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q4" s="186" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="213" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="216" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="129" t="s">
-        <v>150</v>
-      </c>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I5" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J5" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K5" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L5" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M5" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N5" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O5" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P5" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q5" s="133" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C5, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="S5" s="111"/>
-    </row>
-    <row r="6" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="214"/>
-      <c r="C6" s="217"/>
-      <c r="D6" s="134" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" s="135"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="136"/>
-      <c r="H6" s="119"/>
-      <c r="I6" s="119"/>
-      <c r="J6" s="119"/>
-      <c r="K6" s="119"/>
-      <c r="L6" s="119"/>
-      <c r="M6" s="119"/>
-      <c r="N6" s="119"/>
-      <c r="O6" s="119"/>
-      <c r="P6" s="119"/>
-      <c r="Q6" s="137"/>
-      <c r="R6" s="118"/>
-      <c r="S6" s="118"/>
-      <c r="T6" s="118"/>
-      <c r="U6" s="118"/>
-      <c r="V6" s="118"/>
-      <c r="W6" s="118"/>
-      <c r="X6" s="118"/>
-      <c r="Y6" s="118"/>
-      <c r="Z6" s="118"/>
-      <c r="AA6" s="118"/>
-      <c r="AB6" s="118"/>
-      <c r="AC6" s="118"/>
-    </row>
-    <row r="7" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="214"/>
-      <c r="C7" s="194" t="s">
-        <v>92</v>
-      </c>
-      <c r="D7" s="138"/>
-      <c r="E7" s="139" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" s="139" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="140" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" s="127" t="e">
-        <f ca="1">H5-H6</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I7" s="127" t="e">
-        <f ca="1">I5-I6</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J7" s="127" t="e">
-        <f ca="1">J5-J6</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K7" s="127" t="e">
-        <f ca="1">K5-K6</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L7" s="127" t="e">
-        <f ca="1">L5-L6</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M7" s="127" t="e">
-        <f t="shared" ref="M7:Q7" ca="1" si="0">M5-M6</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N7" s="127" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O7" s="127" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P7" s="127" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q7" s="127" t="e">
-        <f t="shared" ca="1" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="214"/>
-      <c r="C8" s="216" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="129" t="s">
-        <v>144</v>
-      </c>
-      <c r="E8" s="130"/>
-      <c r="F8" s="130"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="132" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I8" s="132" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J8" s="132" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K8" s="132" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L8" s="132" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M8" s="132" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N8" s="132" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O8" s="132" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P8" s="132" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q8" s="133" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="214"/>
-      <c r="C9" s="229"/>
-      <c r="D9" s="141" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="142"/>
-      <c r="F9" s="142"/>
-      <c r="G9" s="143"/>
-      <c r="H9" s="117" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="117" t="s">
-        <v>67</v>
-      </c>
-      <c r="J9" s="117" t="s">
-        <v>67</v>
-      </c>
-      <c r="K9" s="117" t="s">
-        <v>67</v>
-      </c>
-      <c r="L9" s="117" t="s">
-        <v>67</v>
-      </c>
-      <c r="M9" s="117" t="s">
-        <v>67</v>
-      </c>
-      <c r="N9" s="117" t="s">
-        <v>67</v>
-      </c>
-      <c r="O9" s="117" t="s">
-        <v>67</v>
-      </c>
-      <c r="P9" s="117" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q9" s="117" t="s">
-        <v>67</v>
-      </c>
-      <c r="R9" s="118"/>
-      <c r="S9" s="118"/>
-      <c r="T9" s="118"/>
-      <c r="U9" s="118"/>
-      <c r="V9" s="118"/>
-      <c r="W9" s="118"/>
-      <c r="X9" s="118"/>
-      <c r="Y9" s="118"/>
-      <c r="Z9" s="118"/>
-      <c r="AA9" s="118"/>
-      <c r="AB9" s="118"/>
-      <c r="AC9" s="118"/>
-    </row>
-    <row r="10" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="214"/>
-      <c r="C10" s="217"/>
-      <c r="D10" s="144" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="135"/>
-      <c r="F10" s="135"/>
-      <c r="G10" s="136"/>
-      <c r="H10" s="121">
-        <v>4.6143497757847536</v>
-      </c>
-      <c r="I10" s="121">
-        <v>4.4887892376681613</v>
-      </c>
-      <c r="J10" s="121">
-        <v>4.5784753363228701</v>
-      </c>
-      <c r="K10" s="121">
-        <v>4.5426008968609866</v>
-      </c>
-      <c r="L10" s="121">
-        <v>4.4887892376681613</v>
-      </c>
-      <c r="M10" s="121">
-        <v>4.4843049327354256</v>
-      </c>
-      <c r="N10" s="121">
-        <v>4.506726457399103</v>
-      </c>
-      <c r="O10" s="121">
-        <v>4.4977578475336326</v>
-      </c>
-      <c r="P10" s="121">
-        <v>4.3991031390134525</v>
-      </c>
-      <c r="Q10" s="122">
-        <v>4.376681614349776</v>
-      </c>
-      <c r="R10" s="118"/>
-      <c r="S10" s="118"/>
-      <c r="T10" s="118"/>
-      <c r="U10" s="118"/>
-      <c r="V10" s="118"/>
-      <c r="W10" s="118"/>
-      <c r="X10" s="118"/>
-      <c r="Y10" s="118"/>
-      <c r="Z10" s="118"/>
-      <c r="AA10" s="118"/>
-      <c r="AB10" s="118"/>
-      <c r="AC10" s="118"/>
-    </row>
-    <row r="11" spans="1:29" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="214"/>
-      <c r="C11" s="123" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" s="138"/>
-      <c r="E11" s="139" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="139"/>
-      <c r="G11" s="140" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11" s="126" t="e">
-        <f>H8-H9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I11" s="127" t="e">
-        <f>I8-I9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J11" s="126" t="e">
-        <f t="shared" ref="J11:Q11" si="1">J8-J9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K11" s="127" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L11" s="126" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M11" s="127" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N11" s="126" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O11" s="127" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P11" s="126" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q11" s="128" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B12" s="214"/>
-      <c r="C12" s="216" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="129" t="s">
-        <v>150</v>
-      </c>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="131"/>
-      <c r="H12" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I12" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J12" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K12" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L12" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M12" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N12" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O12" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P12" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q12" s="133" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C12, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B13" s="214"/>
-      <c r="C13" s="217"/>
-      <c r="D13" s="134" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" s="135"/>
-      <c r="F13" s="135"/>
-      <c r="G13" s="136"/>
-      <c r="H13" s="119"/>
-      <c r="I13" s="119"/>
-      <c r="J13" s="119"/>
-      <c r="K13" s="119"/>
-      <c r="L13" s="119"/>
-      <c r="M13" s="119"/>
-      <c r="N13" s="119"/>
-      <c r="O13" s="119"/>
-      <c r="P13" s="119"/>
-      <c r="Q13" s="137"/>
-      <c r="R13" s="118"/>
-      <c r="S13" s="118"/>
-      <c r="T13" s="118"/>
-      <c r="U13" s="118"/>
-      <c r="V13" s="118"/>
-      <c r="W13" s="118"/>
-      <c r="X13" s="118"/>
-      <c r="Y13" s="118"/>
-      <c r="Z13" s="118"/>
-      <c r="AA13" s="118"/>
-      <c r="AB13" s="118"/>
-      <c r="AC13" s="118"/>
-    </row>
-    <row r="14" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="215"/>
-      <c r="C14" s="193" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="145"/>
-      <c r="E14" s="146" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="146" t="s">
-        <v>70</v>
-      </c>
-      <c r="G14" s="147" t="s">
-        <v>70</v>
-      </c>
-      <c r="H14" s="148" t="e">
-        <f ca="1">H12-H13</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I14" s="148" t="e">
-        <f t="shared" ref="I14:Q14" ca="1" si="2">I12-I13</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J14" s="148" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K14" s="148" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L14" s="148" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M14" s="148" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N14" s="148" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O14" s="148" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P14" s="148" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q14" s="148" t="e">
-        <f t="shared" ca="1" si="2"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="H15" s="105"/>
-      <c r="I15" s="105"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="105"/>
-      <c r="L15" s="105"/>
-      <c r="M15" s="105"/>
-      <c r="N15" s="105"/>
-      <c r="O15" s="105"/>
-      <c r="P15" s="105"/>
-      <c r="Q15" s="105"/>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="B16" s="218" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="219"/>
-      <c r="D16" s="224" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="204" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="205"/>
-      <c r="G16" s="206"/>
-      <c r="H16" s="207" t="s">
-        <v>56</v>
-      </c>
-      <c r="I16" s="208"/>
-      <c r="J16" s="208"/>
-      <c r="K16" s="208"/>
-      <c r="L16" s="208"/>
-      <c r="M16" s="208"/>
-      <c r="N16" s="208"/>
-      <c r="O16" s="208"/>
-      <c r="P16" s="208"/>
-      <c r="Q16" s="209"/>
-    </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B17" s="220"/>
-      <c r="C17" s="221"/>
-      <c r="D17" s="225"/>
-      <c r="E17" s="210" t="s">
-        <v>97</v>
-      </c>
-      <c r="F17" s="211"/>
-      <c r="G17" s="212"/>
-      <c r="H17" s="187"/>
-      <c r="I17" s="188"/>
-      <c r="J17" s="188"/>
-      <c r="K17" s="188"/>
-      <c r="L17" s="188"/>
-      <c r="M17" s="188"/>
-      <c r="N17" s="188"/>
-      <c r="O17" s="188"/>
-      <c r="P17" s="188"/>
-      <c r="Q17" s="189"/>
-    </row>
-    <row r="18" spans="2:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B18" s="222"/>
-      <c r="C18" s="223"/>
-      <c r="D18" s="225"/>
-      <c r="E18" s="181" t="s">
-        <v>141</v>
-      </c>
-      <c r="F18" s="182" t="s">
-        <v>149</v>
-      </c>
-      <c r="G18" s="183" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18" s="190" t="s">
-        <v>58</v>
-      </c>
-      <c r="I18" s="191" t="s">
-        <v>59</v>
-      </c>
-      <c r="J18" s="191" t="s">
-        <v>60</v>
-      </c>
-      <c r="K18" s="191" t="s">
-        <v>139</v>
-      </c>
-      <c r="L18" s="191" t="s">
-        <v>61</v>
-      </c>
-      <c r="M18" s="191" t="s">
-        <v>62</v>
-      </c>
-      <c r="N18" s="191" t="s">
-        <v>63</v>
-      </c>
-      <c r="O18" s="191" t="s">
-        <v>64</v>
-      </c>
-      <c r="P18" s="191" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q18" s="192" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="213" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="216" t="s">
-        <v>147</v>
-      </c>
-      <c r="D19" s="129" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!C"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F19" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!D"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G19" s="149" t="e">
-        <f ca="1">INDIRECT("サマリ!E"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H19" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I19" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J19" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K19" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L19" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M19" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N19" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O19" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P19" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q19" s="133" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C19, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="20" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="214"/>
-      <c r="C20" s="217"/>
-      <c r="D20" s="134" t="s">
-        <v>145</v>
-      </c>
-      <c r="E20" s="119"/>
-      <c r="F20" s="119"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="119"/>
-      <c r="I20" s="119"/>
-      <c r="J20" s="119"/>
-      <c r="K20" s="119"/>
-      <c r="L20" s="119"/>
-      <c r="M20" s="151"/>
-      <c r="N20" s="119"/>
-      <c r="O20" s="119"/>
-      <c r="P20" s="151"/>
-      <c r="Q20" s="137"/>
-      <c r="R20" s="118"/>
-      <c r="S20" s="118"/>
-      <c r="T20" s="118"/>
-      <c r="U20" s="118"/>
-      <c r="V20" s="118"/>
-      <c r="W20" s="118"/>
-      <c r="X20" s="118"/>
-      <c r="Y20" s="118"/>
-      <c r="Z20" s="118"/>
-      <c r="AA20" s="118"/>
-      <c r="AB20" s="118"/>
-    </row>
-    <row r="21" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="214"/>
-      <c r="C21" s="194" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" s="138"/>
-      <c r="E21" s="126" t="e">
-        <f ca="1">E19-E20</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F21" s="126" t="e">
-        <f ca="1">F19-F20</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G21" s="152" t="e">
-        <f ca="1">G19-G20</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H21" s="126" t="e">
-        <f ca="1">H19-H20</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I21" s="126" t="e">
-        <f t="shared" ref="I21:Q21" ca="1" si="3">I19-I20</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J21" s="126" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K21" s="126" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L21" s="126" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M21" s="126" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N21" s="126" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O21" s="126" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P21" s="126" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q21" s="126" t="e">
-        <f t="shared" ca="1" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="214"/>
-      <c r="C22" s="216" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="129" t="s">
-        <v>150</v>
-      </c>
-      <c r="E22" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!C"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F22" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!D"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G22" s="149" t="e">
-        <f ca="1">INDIRECT("サマリ!E"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H22" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I22" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J22" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K22" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L22" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M22" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N22" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O22" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P22" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q22" s="133" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C22, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="23" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="214"/>
-      <c r="C23" s="217"/>
-      <c r="D23" s="134" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23" s="119"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="150"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="119"/>
-      <c r="J23" s="119"/>
-      <c r="K23" s="119"/>
-      <c r="L23" s="119"/>
-      <c r="M23" s="119"/>
-      <c r="N23" s="119"/>
-      <c r="O23" s="119"/>
-      <c r="P23" s="119"/>
-      <c r="Q23" s="137"/>
-      <c r="R23" s="118"/>
-      <c r="S23" s="118"/>
-      <c r="T23" s="118"/>
-      <c r="U23" s="118"/>
-      <c r="V23" s="118"/>
-      <c r="W23" s="118"/>
-      <c r="X23" s="118"/>
-      <c r="Y23" s="118"/>
-      <c r="Z23" s="118"/>
-      <c r="AA23" s="118"/>
-      <c r="AB23" s="118"/>
-    </row>
-    <row r="24" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="214"/>
-      <c r="C24" s="194" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="138"/>
-      <c r="E24" s="126" t="e">
-        <f ca="1">E22-E23</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F24" s="126" t="e">
-        <f t="shared" ref="F24" ca="1" si="4">F22-F23</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G24" s="152" t="e">
-        <f ca="1">G22-G23</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H24" s="126" t="e">
-        <f ca="1">H22-H23</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I24" s="126" t="e">
-        <f t="shared" ref="I24:Q24" ca="1" si="5">I22-I23</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J24" s="126" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K24" s="126" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L24" s="126" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M24" s="126" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N24" s="126" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O24" s="126" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P24" s="126" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q24" s="126" t="e">
-        <f t="shared" ca="1" si="5"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="214"/>
-      <c r="C25" s="216" t="s">
-        <v>153</v>
-      </c>
-      <c r="D25" s="129" t="s">
-        <v>150</v>
-      </c>
-      <c r="E25" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!C"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F25" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!D"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G25" s="149" t="e">
-        <f ca="1">INDIRECT("サマリ!E"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H25" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I25" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J25" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K25" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L25" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M25" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N25" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O25" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P25" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q25" s="133" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C25, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="26" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B26" s="214"/>
-      <c r="C26" s="217"/>
-      <c r="D26" s="134" t="s">
-        <v>145</v>
-      </c>
-      <c r="E26" s="119"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="150"/>
-      <c r="H26" s="119"/>
-      <c r="I26" s="119"/>
-      <c r="J26" s="119"/>
-      <c r="K26" s="119"/>
-      <c r="L26" s="119"/>
-      <c r="M26" s="119"/>
-      <c r="N26" s="119"/>
-      <c r="O26" s="119"/>
-      <c r="P26" s="119"/>
-      <c r="Q26" s="137"/>
-      <c r="R26" s="118"/>
-      <c r="S26" s="118"/>
-      <c r="T26" s="118"/>
-      <c r="U26" s="118"/>
-      <c r="V26" s="118"/>
-      <c r="W26" s="118"/>
-      <c r="X26" s="118"/>
-      <c r="Y26" s="118"/>
-      <c r="Z26" s="118"/>
-      <c r="AA26" s="118"/>
-      <c r="AB26" s="118"/>
-    </row>
-    <row r="27" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="215"/>
-      <c r="C27" s="193" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" s="153"/>
-      <c r="E27" s="154" t="e">
-        <f ca="1">E25-E26</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F27" s="154" t="e">
-        <f t="shared" ref="F27" ca="1" si="6">F25-F26</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G27" s="155" t="e">
-        <f ca="1">G25-G26</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H27" s="154" t="e">
-        <f ca="1">H25-H26</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I27" s="154" t="e">
-        <f t="shared" ref="I27:Q27" ca="1" si="7">I25-I26</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J27" s="154" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K27" s="154" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L27" s="154" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M27" s="154" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N27" s="154" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O27" s="154" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P27" s="154" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q27" s="156" t="e">
-        <f t="shared" ca="1" si="7"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="28" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="H28" s="105"/>
-      <c r="I28" s="105"/>
-      <c r="J28" s="105"/>
-      <c r="K28" s="105"/>
-      <c r="L28" s="105"/>
-      <c r="M28" s="105"/>
-      <c r="N28" s="105"/>
-      <c r="O28" s="105"/>
-      <c r="P28" s="105"/>
-      <c r="Q28" s="105"/>
-    </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="218" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="219"/>
-      <c r="D29" s="224" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" s="204" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" s="205"/>
-      <c r="G29" s="206"/>
-      <c r="H29" s="207" t="s">
-        <v>56</v>
-      </c>
-      <c r="I29" s="208"/>
-      <c r="J29" s="208"/>
-      <c r="K29" s="208"/>
-      <c r="L29" s="208"/>
-      <c r="M29" s="208"/>
-      <c r="N29" s="208"/>
-      <c r="O29" s="208"/>
-      <c r="P29" s="208"/>
-      <c r="Q29" s="209"/>
-    </row>
-    <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="220"/>
-      <c r="C30" s="221"/>
-      <c r="D30" s="225"/>
-      <c r="E30" s="210" t="s">
-        <v>97</v>
-      </c>
-      <c r="F30" s="211"/>
-      <c r="G30" s="212"/>
-      <c r="H30" s="187"/>
-      <c r="I30" s="188"/>
-      <c r="J30" s="188"/>
-      <c r="K30" s="188"/>
-      <c r="L30" s="188"/>
-      <c r="M30" s="188"/>
-      <c r="N30" s="188"/>
-      <c r="O30" s="188"/>
-      <c r="P30" s="188"/>
-      <c r="Q30" s="189"/>
-    </row>
-    <row r="31" spans="2:28" ht="36.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="222"/>
-      <c r="C31" s="223"/>
-      <c r="D31" s="225"/>
-      <c r="E31" s="181" t="s">
-        <v>141</v>
-      </c>
-      <c r="F31" s="182" t="s">
-        <v>149</v>
-      </c>
-      <c r="G31" s="183" t="s">
-        <v>57</v>
-      </c>
-      <c r="H31" s="190" t="s">
-        <v>58</v>
-      </c>
-      <c r="I31" s="191" t="s">
-        <v>59</v>
-      </c>
-      <c r="J31" s="191" t="s">
-        <v>60</v>
-      </c>
-      <c r="K31" s="191" t="s">
-        <v>139</v>
-      </c>
-      <c r="L31" s="191" t="s">
-        <v>61</v>
-      </c>
-      <c r="M31" s="191" t="s">
-        <v>62</v>
-      </c>
-      <c r="N31" s="191" t="s">
-        <v>63</v>
-      </c>
-      <c r="O31" s="191" t="s">
-        <v>64</v>
-      </c>
-      <c r="P31" s="191" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q31" s="192" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B32" s="213" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="216" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" s="129" t="s">
-        <v>150</v>
-      </c>
-      <c r="E32" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!C"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F32" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!D"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G32" s="149" t="e">
-        <f ca="1">INDIRECT("サマリ!E"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H32" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I32" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J32" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K32" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L32" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M32" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N32" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O32" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P32" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q32" s="133" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C32, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="33" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B33" s="214"/>
-      <c r="C33" s="217"/>
-      <c r="D33" s="134" t="s">
-        <v>145</v>
-      </c>
-      <c r="E33" s="119"/>
-      <c r="F33" s="119"/>
-      <c r="G33" s="150"/>
-      <c r="H33" s="119"/>
-      <c r="I33" s="119"/>
-      <c r="J33" s="119"/>
-      <c r="K33" s="119"/>
-      <c r="L33" s="119"/>
-      <c r="M33" s="119"/>
-      <c r="N33" s="119"/>
-      <c r="O33" s="119"/>
-      <c r="P33" s="119"/>
-      <c r="Q33" s="137"/>
-      <c r="R33" s="118"/>
-      <c r="S33" s="118"/>
-      <c r="T33" s="118"/>
-      <c r="U33" s="118"/>
-      <c r="V33" s="118"/>
-      <c r="W33" s="118"/>
-      <c r="X33" s="118"/>
-      <c r="Y33" s="118"/>
-      <c r="Z33" s="118"/>
-      <c r="AA33" s="118"/>
-      <c r="AB33" s="118"/>
-    </row>
-    <row r="34" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B34" s="214"/>
-      <c r="C34" s="194" t="s">
-        <v>92</v>
-      </c>
-      <c r="D34" s="157"/>
-      <c r="E34" s="158" t="e">
-        <f ca="1">E32-E33</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F34" s="159" t="e">
-        <f ca="1">F32-F33</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G34" s="152" t="e">
-        <f ca="1">G32-G33</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H34" s="126" t="e">
-        <f ca="1">H32-H33</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I34" s="126" t="e">
-        <f t="shared" ref="I34:Q34" ca="1" si="8">I32-I33</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J34" s="126" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K34" s="126" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L34" s="126" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M34" s="126" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N34" s="126" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O34" s="126" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P34" s="126" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q34" s="126" t="e">
-        <f t="shared" ca="1" si="8"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="214"/>
-      <c r="C35" s="216" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="129" t="s">
-        <v>150</v>
-      </c>
-      <c r="E35" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!C"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F35" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!D"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G35" s="149" t="e">
-        <f ca="1">INDIRECT("サマリ!E"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H35" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I35" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J35" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K35" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L35" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M35" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N35" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O35" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P35" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q35" s="133" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C35, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="36" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="214"/>
-      <c r="C36" s="217"/>
-      <c r="D36" s="134" t="s">
-        <v>145</v>
-      </c>
-      <c r="E36" s="119"/>
-      <c r="F36" s="119"/>
-      <c r="G36" s="150"/>
-      <c r="H36" s="151"/>
-      <c r="I36" s="151"/>
-      <c r="J36" s="151"/>
-      <c r="K36" s="151"/>
-      <c r="L36" s="151"/>
-      <c r="M36" s="151"/>
-      <c r="N36" s="151"/>
-      <c r="O36" s="151"/>
-      <c r="P36" s="151"/>
-      <c r="Q36" s="160"/>
-      <c r="R36" s="118"/>
-      <c r="S36" s="118"/>
-      <c r="T36" s="118"/>
-      <c r="U36" s="118"/>
-      <c r="V36" s="118"/>
-      <c r="W36" s="118"/>
-      <c r="X36" s="118"/>
-      <c r="Y36" s="118"/>
-      <c r="Z36" s="118"/>
-      <c r="AA36" s="118"/>
-      <c r="AB36" s="118"/>
-    </row>
-    <row r="37" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B37" s="214"/>
-      <c r="C37" s="194" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37" s="157"/>
-      <c r="E37" s="158" t="e">
-        <f ca="1">E35-E36</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F37" s="159" t="e">
-        <f ca="1">F35-F36</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G37" s="152" t="e">
-        <f ca="1">G35-G36</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H37" s="126" t="e">
-        <f ca="1">H35-H36</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I37" s="126" t="e">
-        <f t="shared" ref="I37:Q37" ca="1" si="9">I35-I36</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J37" s="126" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K37" s="126" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L37" s="126" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M37" s="126" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N37" s="126" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O37" s="126" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P37" s="126" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q37" s="126" t="e">
-        <f t="shared" ca="1" si="9"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="214"/>
-      <c r="C38" s="216" t="s">
-        <v>94</v>
-      </c>
-      <c r="D38" s="129" t="s">
-        <v>150</v>
-      </c>
-      <c r="E38" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!C"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F38" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!D"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G38" s="149" t="e">
-        <f ca="1">INDIRECT("サマリ!E"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H38" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I38" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J38" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K38" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L38" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M38" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N38" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O38" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P38" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q38" s="133" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C38, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="39" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="214"/>
-      <c r="C39" s="217"/>
-      <c r="D39" s="134" t="s">
-        <v>145</v>
-      </c>
-      <c r="E39" s="119"/>
-      <c r="F39" s="119"/>
-      <c r="G39" s="150"/>
-      <c r="H39" s="151"/>
-      <c r="I39" s="151"/>
-      <c r="J39" s="151"/>
-      <c r="K39" s="151"/>
-      <c r="L39" s="151"/>
-      <c r="M39" s="151"/>
-      <c r="N39" s="151"/>
-      <c r="O39" s="151"/>
-      <c r="P39" s="151"/>
-      <c r="Q39" s="160"/>
-      <c r="R39" s="118"/>
-      <c r="S39" s="118"/>
-      <c r="T39" s="118"/>
-      <c r="U39" s="118"/>
-      <c r="V39" s="118"/>
-      <c r="W39" s="118"/>
-      <c r="X39" s="118"/>
-      <c r="Y39" s="118"/>
-      <c r="Z39" s="118"/>
-      <c r="AA39" s="118"/>
-      <c r="AB39" s="118"/>
-    </row>
-    <row r="40" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="214"/>
-      <c r="C40" s="194" t="s">
-        <v>92</v>
-      </c>
-      <c r="D40" s="161"/>
-      <c r="E40" s="158" t="e">
-        <f ca="1">E38-E39</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F40" s="159" t="e">
-        <f ca="1">F38-F39</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G40" s="152" t="e">
-        <f ca="1">G38-G39</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H40" s="162" t="e">
-        <f ca="1">H38-H39</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I40" s="162" t="e">
-        <f t="shared" ref="I40:Q40" ca="1" si="10">I38-I39</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J40" s="162" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K40" s="162" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L40" s="162" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M40" s="162" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N40" s="162" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O40" s="162" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P40" s="162" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q40" s="162" t="e">
-        <f t="shared" ca="1" si="10"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="214"/>
-      <c r="C41" s="216" t="s">
-        <v>154</v>
-      </c>
-      <c r="D41" s="129" t="s">
-        <v>150</v>
-      </c>
-      <c r="E41" s="163"/>
-      <c r="F41" s="164"/>
-      <c r="G41" s="131"/>
-      <c r="H41" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!F"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I41" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!G"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J41" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!H"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K41" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!I"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L41" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!J"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M41" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!K"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N41" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!L"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O41" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!M"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P41" s="132" t="e">
-        <f ca="1">INDIRECT("サマリ!N"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q41" s="133" t="e">
-        <f ca="1">INDIRECT("サマリ!O"&amp;MATCH(C41, サマリ!B:B, 0))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="42" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B42" s="214"/>
-      <c r="C42" s="217"/>
-      <c r="D42" s="134" t="s">
-        <v>145</v>
-      </c>
-      <c r="E42" s="165"/>
-      <c r="F42" s="166"/>
-      <c r="G42" s="136"/>
-      <c r="H42" s="151"/>
-      <c r="I42" s="151"/>
-      <c r="J42" s="151"/>
-      <c r="K42" s="151"/>
-      <c r="L42" s="151"/>
-      <c r="M42" s="151"/>
-      <c r="N42" s="151"/>
-      <c r="O42" s="151"/>
-      <c r="P42" s="151"/>
-      <c r="Q42" s="160"/>
-      <c r="R42" s="118"/>
-      <c r="S42" s="118"/>
-      <c r="T42" s="118"/>
-      <c r="U42" s="118"/>
-      <c r="V42" s="118"/>
-      <c r="W42" s="118"/>
-      <c r="X42" s="118"/>
-      <c r="Y42" s="118"/>
-      <c r="Z42" s="118"/>
-      <c r="AA42" s="118"/>
-      <c r="AB42" s="118"/>
-    </row>
-    <row r="43" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="215"/>
-      <c r="C43" s="193" t="s">
-        <v>92</v>
-      </c>
-      <c r="D43" s="167"/>
-      <c r="E43" s="168" t="s">
-        <v>70</v>
-      </c>
-      <c r="F43" s="169" t="s">
-        <v>70</v>
-      </c>
-      <c r="G43" s="170" t="s">
-        <v>70</v>
-      </c>
-      <c r="H43" s="171" t="e">
-        <f ca="1">H41-H42</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I43" s="171" t="e">
-        <f t="shared" ref="I43:Q43" ca="1" si="11">I41-I42</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J43" s="171" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K43" s="171" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L43" s="171" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M43" s="171" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N43" s="171" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O43" s="171" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P43" s="171" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q43" s="171" t="e">
-        <f t="shared" ca="1" si="11"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="C45" s="104" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" s="172" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="C46" s="173"/>
-      <c r="D46" s="174" t="s">
-        <v>89</v>
-      </c>
-      <c r="E46" s="175"/>
-      <c r="F46" s="175"/>
-      <c r="G46" s="176"/>
-      <c r="H46" s="176" t="s">
-        <v>78</v>
-      </c>
-      <c r="I46" s="176"/>
-      <c r="J46" s="176"/>
-      <c r="K46" s="176"/>
-      <c r="L46" s="176"/>
-      <c r="M46" s="176"/>
-      <c r="N46" s="176"/>
-      <c r="O46" s="176"/>
-      <c r="P46" s="176"/>
-      <c r="Q46" s="176"/>
-      <c r="R46" s="176"/>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="D47" s="174" t="s">
-        <v>88</v>
-      </c>
-      <c r="E47" s="175"/>
-      <c r="F47" s="175"/>
-      <c r="G47" s="176"/>
-      <c r="H47" s="176" t="s">
-        <v>78</v>
-      </c>
-      <c r="I47" s="176"/>
-      <c r="J47" s="176"/>
-      <c r="K47" s="176"/>
-      <c r="L47" s="176"/>
-      <c r="M47" s="176"/>
-      <c r="N47" s="176"/>
-      <c r="O47" s="176"/>
-      <c r="P47" s="176"/>
-      <c r="Q47" s="176"/>
-      <c r="R47" s="176"/>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="D48" s="172" t="s">
-        <v>87</v>
-      </c>
-      <c r="E48" s="175"/>
-      <c r="F48" s="175"/>
-      <c r="G48" s="176"/>
-      <c r="H48" s="176" t="s">
-        <v>78</v>
-      </c>
-      <c r="I48" s="176"/>
-      <c r="L48" s="176"/>
-      <c r="M48" s="176"/>
-      <c r="N48" s="176"/>
-      <c r="O48" s="176"/>
-      <c r="P48" s="176"/>
-      <c r="Q48" s="176"/>
-      <c r="R48" s="176"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D49" s="174" t="s">
-        <v>86</v>
-      </c>
-      <c r="E49" s="175"/>
-      <c r="F49" s="175"/>
-      <c r="G49" s="176"/>
-      <c r="H49" s="176" t="s">
-        <v>78</v>
-      </c>
-      <c r="I49" s="176"/>
-      <c r="J49" s="176"/>
-      <c r="K49" s="176"/>
-      <c r="L49" s="176"/>
-      <c r="M49" s="176"/>
-      <c r="N49" s="176"/>
-      <c r="O49" s="176"/>
-      <c r="P49" s="176"/>
-      <c r="Q49" s="176"/>
-      <c r="R49" s="176"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D50" s="174" t="s">
-        <v>85</v>
-      </c>
-      <c r="E50" s="175"/>
-      <c r="F50" s="175"/>
-      <c r="G50" s="176"/>
-      <c r="H50" s="176"/>
-      <c r="I50" s="176"/>
-      <c r="J50" s="176"/>
-      <c r="K50" s="176"/>
-      <c r="L50" s="176"/>
-      <c r="M50" s="176"/>
-      <c r="N50" s="176"/>
-      <c r="O50" s="176"/>
-      <c r="P50" s="176"/>
-      <c r="Q50" s="176"/>
-      <c r="R50" s="176"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D51" s="174" t="s">
-        <v>84</v>
-      </c>
-      <c r="E51" s="175"/>
-      <c r="F51" s="175"/>
-      <c r="G51" s="176"/>
-      <c r="H51" s="176" t="s">
-        <v>78</v>
-      </c>
-      <c r="I51" s="176"/>
-      <c r="J51" s="176"/>
-      <c r="K51" s="176"/>
-      <c r="L51" s="176"/>
-      <c r="M51" s="176"/>
-      <c r="N51" s="176"/>
-      <c r="O51" s="176"/>
-      <c r="P51" s="176"/>
-      <c r="Q51" s="176"/>
-      <c r="R51" s="176"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D52" s="174" t="s">
-        <v>83</v>
-      </c>
-      <c r="E52" s="175"/>
-      <c r="F52" s="175"/>
-      <c r="G52" s="176"/>
-      <c r="H52" s="176" t="s">
-        <v>78</v>
-      </c>
-      <c r="I52" s="176"/>
-      <c r="J52" s="176"/>
-      <c r="K52" s="176"/>
-      <c r="L52" s="176"/>
-      <c r="M52" s="176"/>
-      <c r="N52" s="176"/>
-      <c r="O52" s="176"/>
-      <c r="P52" s="176"/>
-      <c r="Q52" s="176"/>
-      <c r="R52" s="176"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D53" s="177" t="s">
-        <v>82</v>
-      </c>
-      <c r="E53" s="175"/>
-      <c r="F53" s="175"/>
-      <c r="G53" s="176"/>
-      <c r="H53" s="176" t="s">
-        <v>78</v>
-      </c>
-      <c r="I53" s="176"/>
-      <c r="J53" s="176"/>
-      <c r="K53" s="176"/>
-      <c r="L53" s="176"/>
-      <c r="M53" s="176"/>
-      <c r="N53" s="176"/>
-      <c r="O53" s="176"/>
-      <c r="P53" s="176"/>
-      <c r="Q53" s="176"/>
-      <c r="R53" s="176"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D54" s="174" t="s">
-        <v>81</v>
-      </c>
-      <c r="E54" s="175"/>
-      <c r="F54" s="175"/>
-      <c r="G54" s="176"/>
-      <c r="H54" s="176" t="s">
-        <v>78</v>
-      </c>
-      <c r="I54" s="176"/>
-      <c r="J54" s="176"/>
-      <c r="K54" s="176"/>
-      <c r="L54" s="176"/>
-      <c r="M54" s="176"/>
-      <c r="N54" s="176"/>
-      <c r="O54" s="176"/>
-      <c r="P54" s="176"/>
-      <c r="Q54" s="176"/>
-      <c r="R54" s="176"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D55" s="174" t="s">
-        <v>80</v>
-      </c>
-      <c r="E55" s="175"/>
-      <c r="F55" s="175"/>
-      <c r="G55" s="176"/>
-      <c r="H55" s="176" t="s">
-        <v>78</v>
-      </c>
-      <c r="I55" s="176"/>
-      <c r="J55" s="176"/>
-      <c r="K55" s="176"/>
-      <c r="L55" s="176"/>
-      <c r="M55" s="176"/>
-      <c r="N55" s="176"/>
-      <c r="O55" s="176"/>
-      <c r="P55" s="176"/>
-      <c r="Q55" s="176"/>
-      <c r="R55" s="176"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="D56" s="174" t="s">
-        <v>79</v>
-      </c>
-      <c r="E56" s="175"/>
-      <c r="F56" s="175"/>
-      <c r="G56" s="176"/>
-      <c r="H56" s="176" t="s">
-        <v>78</v>
-      </c>
-      <c r="I56" s="176"/>
-      <c r="J56" s="176"/>
-      <c r="K56" s="176"/>
-      <c r="L56" s="176"/>
-      <c r="M56" s="176"/>
-      <c r="N56" s="176"/>
-      <c r="O56" s="176"/>
-      <c r="P56" s="176"/>
-      <c r="Q56" s="176"/>
-      <c r="R56" s="176"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="C58" s="104" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="C59" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="E59" s="175"/>
-      <c r="F59" s="175"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="C60" s="104" t="s">
-        <v>75</v>
-      </c>
-      <c r="E60" s="175"/>
-      <c r="F60" s="175"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="C61" s="104" t="s">
-        <v>142</v>
-      </c>
-      <c r="E61" s="175"/>
-      <c r="F61" s="175"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="C63" s="104" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.45">
-      <c r="C64" s="104" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C65" s="104" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:Q2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B5:B14"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="B16:C18"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:Q16"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="B32:B43"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="B29:C31"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="H29:Q29"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="B19:B27"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C22:C23"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="H5:Q6">
-    <cfRule type="cellIs" dxfId="35" priority="1" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H8:Q8">
-    <cfRule type="cellIs" dxfId="34" priority="18" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H9:Q9">
-    <cfRule type="cellIs" dxfId="33" priority="19" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10:Q10">
-    <cfRule type="cellIs" dxfId="32" priority="20" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12:Q13">
-    <cfRule type="cellIs" dxfId="31" priority="4" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H19:Q20">
-    <cfRule type="cellIs" dxfId="30" priority="16" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:Q22">
-    <cfRule type="cellIs" dxfId="29" priority="10" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23:Q23 H39:Q39 H42:Q42">
-    <cfRule type="cellIs" dxfId="28" priority="21" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25:Q26">
-    <cfRule type="cellIs" dxfId="27" priority="9" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32:Q33">
-    <cfRule type="cellIs" dxfId="26" priority="8" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H35:Q36">
-    <cfRule type="cellIs" dxfId="25" priority="7" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H38:Q38">
-    <cfRule type="cellIs" dxfId="24" priority="6" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H41:Q41">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="17" id="{69DAD745-8B3F-426A-85FA-E4560827F22D}">
-            <x14:iconSet iconSet="3Arrows" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>-0.25</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0.25</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H11:P11 H7:Q7 H14:Q14 H21:Q21 H24:Q24 H27:Q27 H34:Q34 H40:Q40 H37:Q37 H43:Q43</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5C06947-9AD3-4764-A00F-59E09793C545}">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
@@ -5844,40 +2855,40 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="230" t="s">
+      <c r="B2" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="231"/>
-      <c r="D2" s="242" t="s">
+      <c r="C2" s="117"/>
+      <c r="D2" s="125" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="250" t="s">
+      <c r="E2" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="251"/>
-      <c r="G2" s="252"/>
-      <c r="H2" s="244" t="s">
+      <c r="F2" s="134"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="245"/>
-      <c r="J2" s="245"/>
-      <c r="K2" s="245"/>
-      <c r="L2" s="245"/>
-      <c r="M2" s="245"/>
-      <c r="N2" s="245"/>
-      <c r="O2" s="245"/>
-      <c r="P2" s="245"/>
-      <c r="Q2" s="246"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="129"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="232"/>
-      <c r="C3" s="233"/>
-      <c r="D3" s="243"/>
-      <c r="E3" s="247" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="248"/>
-      <c r="G3" s="249"/>
+      <c r="B3" s="118"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="131"/>
+      <c r="G3" s="132"/>
       <c r="H3" s="22"/>
       <c r="I3" s="21"/>
       <c r="J3" s="21"/>
@@ -5890,14 +2901,14 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="234"/>
-      <c r="C4" s="235"/>
-      <c r="D4" s="243"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="126"/>
       <c r="E4" s="85" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F4" s="90" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G4" s="86" t="s">
         <v>57</v>
@@ -5912,7 +2923,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L4" s="24" t="s">
         <v>61</v>
@@ -5934,14 +2945,14 @@
       </c>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B5" s="239" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="236" t="s">
-        <v>138</v>
+      <c r="B5" s="122" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="113" t="s">
+        <v>137</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
@@ -5987,14 +2998,14 @@
         <v>#REF!</v>
       </c>
       <c r="S5" s="63" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B6" s="240"/>
-      <c r="C6" s="237"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="114"/>
       <c r="D6" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E6" s="27"/>
       <c r="F6" s="27"/>
@@ -6031,7 +3042,7 @@
       </c>
       <c r="R6" s="19"/>
       <c r="S6" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="T6" s="19"/>
       <c r="U6" s="19"/>
@@ -6045,10 +3056,10 @@
       <c r="AC6" s="19"/>
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="240"/>
-      <c r="C7" s="238"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="115"/>
       <c r="D7" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
@@ -6097,17 +3108,17 @@
       <c r="AC7" s="19"/>
     </row>
     <row r="8" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="240"/>
+      <c r="B8" s="123"/>
       <c r="C8" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D8" s="57"/>
       <c r="E8" s="61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F8" s="61"/>
       <c r="G8" s="62" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H8" s="42" t="e">
         <f>H5-H6</f>
@@ -6151,12 +3162,12 @@
       </c>
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="240"/>
-      <c r="C9" s="236" t="s">
-        <v>102</v>
+      <c r="B9" s="123"/>
+      <c r="C9" s="113" t="s">
+        <v>101</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="30"/>
@@ -6203,43 +3214,43 @@
       </c>
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="240"/>
-      <c r="C10" s="237"/>
+      <c r="B10" s="123"/>
+      <c r="C10" s="114"/>
       <c r="D10" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="27"/>
       <c r="G10" s="28"/>
       <c r="H10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q10" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R10" s="19"/>
       <c r="S10" s="19"/>
@@ -6255,10 +3266,10 @@
       <c r="AC10" s="19"/>
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="240"/>
-      <c r="C11" s="238"/>
+      <c r="B11" s="123"/>
+      <c r="C11" s="115"/>
       <c r="D11" s="34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11" s="53"/>
       <c r="F11" s="53"/>
@@ -6307,17 +3318,17 @@
       <c r="AC11" s="19"/>
     </row>
     <row r="12" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="240"/>
+      <c r="B12" s="123"/>
       <c r="C12" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" s="57"/>
       <c r="E12" s="61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F12" s="61"/>
       <c r="G12" s="62" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H12" s="42" t="e">
         <f>H9-H10</f>
@@ -6361,12 +3372,12 @@
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B13" s="240"/>
-      <c r="C13" s="236" t="s">
+      <c r="B13" s="123"/>
+      <c r="C13" s="113" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="33" t="s">
         <v>143</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>144</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="30"/>
@@ -6413,10 +3424,10 @@
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B14" s="240"/>
-      <c r="C14" s="237"/>
+      <c r="B14" s="123"/>
+      <c r="C14" s="114"/>
       <c r="D14" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E14" s="27"/>
       <c r="F14" s="27"/>
@@ -6465,10 +3476,10 @@
       <c r="AC14" s="19"/>
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="240"/>
-      <c r="C15" s="238"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="115"/>
       <c r="D15" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E15" s="53"/>
       <c r="F15" s="53"/>
@@ -6517,17 +3528,17 @@
       <c r="AC15" s="19"/>
     </row>
     <row r="16" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="241"/>
+      <c r="B16" s="124"/>
       <c r="C16" s="32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D16" s="55"/>
       <c r="E16" s="59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F16" s="59"/>
       <c r="G16" s="60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H16" s="51" t="e">
         <f>H13-H14</f>
@@ -6583,40 +3594,40 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="230" t="s">
+      <c r="B18" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="231"/>
-      <c r="D18" s="242" t="s">
+      <c r="C18" s="117"/>
+      <c r="D18" s="125" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="250" t="s">
+      <c r="E18" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="251"/>
-      <c r="G18" s="252"/>
-      <c r="H18" s="256" t="s">
+      <c r="F18" s="134"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="139" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="257"/>
-      <c r="J18" s="257"/>
-      <c r="K18" s="257"/>
-      <c r="L18" s="257"/>
-      <c r="M18" s="257"/>
-      <c r="N18" s="257"/>
-      <c r="O18" s="257"/>
-      <c r="P18" s="257"/>
-      <c r="Q18" s="258"/>
+      <c r="I18" s="140"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="140"/>
+      <c r="L18" s="140"/>
+      <c r="M18" s="140"/>
+      <c r="N18" s="140"/>
+      <c r="O18" s="140"/>
+      <c r="P18" s="140"/>
+      <c r="Q18" s="141"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="232"/>
-      <c r="C19" s="233"/>
-      <c r="D19" s="243"/>
-      <c r="E19" s="247" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="248"/>
-      <c r="G19" s="249"/>
+      <c r="B19" s="118"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="131"/>
+      <c r="G19" s="132"/>
       <c r="H19" s="67"/>
       <c r="I19" s="68"/>
       <c r="J19" s="68"/>
@@ -6629,14 +3640,14 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="234"/>
-      <c r="C20" s="235"/>
-      <c r="D20" s="243"/>
+      <c r="B20" s="120"/>
+      <c r="C20" s="121"/>
+      <c r="D20" s="126"/>
       <c r="E20" s="85" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F20" s="90" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G20" s="86" t="s">
         <v>57</v>
@@ -6651,7 +3662,7 @@
         <v>60</v>
       </c>
       <c r="K20" s="71" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L20" s="71" t="s">
         <v>61</v>
@@ -6673,14 +3684,14 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B21" s="239" t="s">
-        <v>101</v>
-      </c>
-      <c r="C21" s="236" t="s">
+      <c r="B21" s="122" t="s">
         <v>100</v>
       </c>
+      <c r="C21" s="113" t="s">
+        <v>99</v>
+      </c>
       <c r="D21" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E21" s="64" t="e">
         <f>#REF!</f>
@@ -6736,10 +3747,10 @@
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="240"/>
-      <c r="C22" s="237"/>
+      <c r="B22" s="123"/>
+      <c r="C22" s="114"/>
       <c r="D22" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E22" s="78">
         <v>93.333333333333329</v>
@@ -6791,10 +3802,10 @@
       <c r="AB22" s="19"/>
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="240"/>
-      <c r="C23" s="238"/>
+      <c r="B23" s="123"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E23" s="79">
         <v>93.706896551724142</v>
@@ -6846,9 +3857,9 @@
       <c r="AB23" s="19"/>
     </row>
     <row r="24" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="240"/>
+      <c r="B24" s="123"/>
       <c r="C24" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D24" s="57"/>
       <c r="E24" s="42" t="e">
@@ -6902,12 +3913,12 @@
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B25" s="240"/>
-      <c r="C25" s="236" t="s">
-        <v>99</v>
+      <c r="B25" s="123"/>
+      <c r="C25" s="113" t="s">
+        <v>98</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E25" s="64" t="e">
         <f>#REF!</f>
@@ -6963,10 +3974,10 @@
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B26" s="240"/>
-      <c r="C26" s="237"/>
+      <c r="B26" s="123"/>
+      <c r="C26" s="114"/>
       <c r="D26" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E26" s="78">
         <v>90.340501792114694</v>
@@ -7018,10 +4029,10 @@
       <c r="AB26" s="19"/>
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="240"/>
-      <c r="C27" s="238"/>
+      <c r="B27" s="123"/>
+      <c r="C27" s="115"/>
       <c r="D27" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E27" s="79">
         <v>88.879310344827587</v>
@@ -7073,9 +4084,9 @@
       <c r="AB27" s="19"/>
     </row>
     <row r="28" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="240"/>
+      <c r="B28" s="123"/>
       <c r="C28" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D28" s="57"/>
       <c r="E28" s="42" t="e">
@@ -7129,12 +4140,12 @@
       </c>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="240"/>
-      <c r="C29" s="236" t="s">
-        <v>98</v>
+      <c r="B29" s="123"/>
+      <c r="C29" s="113" t="s">
+        <v>97</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E29" s="64" t="e">
         <f>#REF!</f>
@@ -7190,10 +4201,10 @@
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="240"/>
-      <c r="C30" s="237"/>
+      <c r="B30" s="123"/>
+      <c r="C30" s="114"/>
       <c r="D30" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E30" s="78">
         <v>94.086021505376351</v>
@@ -7245,10 +4256,10 @@
       <c r="AB30" s="19"/>
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="240"/>
-      <c r="C31" s="238"/>
+      <c r="B31" s="123"/>
+      <c r="C31" s="115"/>
       <c r="D31" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E31" s="79">
         <v>94.137931034482762</v>
@@ -7300,9 +4311,9 @@
       <c r="AB31" s="19"/>
     </row>
     <row r="32" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="241"/>
+      <c r="B32" s="124"/>
       <c r="C32" s="32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D32" s="55"/>
       <c r="E32" s="51" t="e">
@@ -7368,40 +4379,40 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="230" t="s">
+      <c r="B34" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="231"/>
-      <c r="D34" s="242" t="s">
+      <c r="C34" s="117"/>
+      <c r="D34" s="125" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="250" t="s">
+      <c r="E34" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="F34" s="251"/>
-      <c r="G34" s="252"/>
-      <c r="H34" s="256" t="s">
+      <c r="F34" s="134"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="139" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="257"/>
-      <c r="J34" s="257"/>
-      <c r="K34" s="257"/>
-      <c r="L34" s="257"/>
-      <c r="M34" s="257"/>
-      <c r="N34" s="257"/>
-      <c r="O34" s="257"/>
-      <c r="P34" s="257"/>
-      <c r="Q34" s="258"/>
+      <c r="I34" s="140"/>
+      <c r="J34" s="140"/>
+      <c r="K34" s="140"/>
+      <c r="L34" s="140"/>
+      <c r="M34" s="140"/>
+      <c r="N34" s="140"/>
+      <c r="O34" s="140"/>
+      <c r="P34" s="140"/>
+      <c r="Q34" s="141"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="232"/>
-      <c r="C35" s="233"/>
-      <c r="D35" s="243"/>
-      <c r="E35" s="247" t="s">
-        <v>97</v>
-      </c>
-      <c r="F35" s="248"/>
-      <c r="G35" s="249"/>
+      <c r="B35" s="118"/>
+      <c r="C35" s="119"/>
+      <c r="D35" s="126"/>
+      <c r="E35" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="F35" s="131"/>
+      <c r="G35" s="132"/>
       <c r="H35" s="67"/>
       <c r="I35" s="68"/>
       <c r="J35" s="68"/>
@@ -7414,14 +4425,14 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="234"/>
-      <c r="C36" s="235"/>
-      <c r="D36" s="243"/>
+      <c r="B36" s="120"/>
+      <c r="C36" s="121"/>
+      <c r="D36" s="126"/>
       <c r="E36" s="85" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F36" s="90" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G36" s="86" t="s">
         <v>57</v>
@@ -7436,7 +4447,7 @@
         <v>60</v>
       </c>
       <c r="K36" s="71" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L36" s="71" t="s">
         <v>61</v>
@@ -7458,14 +4469,14 @@
       </c>
     </row>
     <row r="37" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B37" s="239" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="236" t="s">
+      <c r="B37" s="122" t="s">
         <v>95</v>
       </c>
+      <c r="C37" s="113" t="s">
+        <v>94</v>
+      </c>
       <c r="D37" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E37" s="64" t="e">
         <f>#REF!</f>
@@ -7521,10 +4532,10 @@
       </c>
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B38" s="240"/>
-      <c r="C38" s="237"/>
+      <c r="B38" s="123"/>
+      <c r="C38" s="114"/>
       <c r="D38" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E38" s="78">
         <v>90.663082437275989</v>
@@ -7576,10 +4587,10 @@
       <c r="AB38" s="19"/>
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B39" s="240"/>
-      <c r="C39" s="238"/>
+      <c r="B39" s="123"/>
+      <c r="C39" s="115"/>
       <c r="D39" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E39" s="79">
         <v>90.193965517241381</v>
@@ -7631,9 +4642,9 @@
       <c r="AB39" s="19"/>
     </row>
     <row r="40" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="240"/>
+      <c r="B40" s="123"/>
       <c r="C40" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D40" s="37"/>
       <c r="E40" s="39" t="e">
@@ -7687,12 +4698,12 @@
       </c>
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B41" s="240"/>
-      <c r="C41" s="236" t="s">
-        <v>80</v>
+      <c r="B41" s="123"/>
+      <c r="C41" s="113" t="s">
+        <v>79</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E41" s="64" t="e">
         <f>#REF!</f>
@@ -7748,10 +4759,10 @@
       </c>
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B42" s="240"/>
-      <c r="C42" s="237"/>
+      <c r="B42" s="123"/>
+      <c r="C42" s="114"/>
       <c r="D42" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E42" s="78">
         <v>87.354838709677423</v>
@@ -7803,10 +4814,10 @@
       <c r="AB42" s="19"/>
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B43" s="240"/>
-      <c r="C43" s="238"/>
+      <c r="B43" s="123"/>
+      <c r="C43" s="115"/>
       <c r="D43" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E43" s="79">
         <v>87.482758620689651</v>
@@ -7858,9 +4869,9 @@
       <c r="AB43" s="19"/>
     </row>
     <row r="44" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B44" s="240"/>
+      <c r="B44" s="123"/>
       <c r="C44" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D44" s="37"/>
       <c r="E44" s="39" t="e">
@@ -7914,12 +4925,12 @@
       </c>
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B45" s="240"/>
-      <c r="C45" s="236" t="s">
-        <v>94</v>
+      <c r="B45" s="123"/>
+      <c r="C45" s="113" t="s">
+        <v>93</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E45" s="64" t="e">
         <f>#REF!</f>
@@ -7975,10 +4986,10 @@
       </c>
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B46" s="240"/>
-      <c r="C46" s="237"/>
+      <c r="B46" s="123"/>
+      <c r="C46" s="114"/>
       <c r="D46" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E46" s="78">
         <v>78.709677419354833</v>
@@ -8030,10 +5041,10 @@
       <c r="AB46" s="19"/>
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B47" s="240"/>
-      <c r="C47" s="238"/>
+      <c r="B47" s="123"/>
+      <c r="C47" s="115"/>
       <c r="D47" s="83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E47" s="79">
         <v>76.681034482758619</v>
@@ -8085,9 +5096,9 @@
       <c r="AB47" s="19"/>
     </row>
     <row r="48" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B48" s="240"/>
+      <c r="B48" s="123"/>
       <c r="C48" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D48" s="44"/>
       <c r="E48" s="39" t="e">
@@ -8141,14 +5152,14 @@
       </c>
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B49" s="240"/>
-      <c r="C49" s="236" t="s">
-        <v>93</v>
+      <c r="B49" s="123"/>
+      <c r="C49" s="113" t="s">
+        <v>92</v>
       </c>
       <c r="D49" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="E49" s="253"/>
+        <v>143</v>
+      </c>
+      <c r="E49" s="136"/>
       <c r="F49" s="87"/>
       <c r="G49" s="31"/>
       <c r="H49" s="64" t="e">
@@ -8193,12 +5204,12 @@
       </c>
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="240"/>
-      <c r="C50" s="237"/>
+      <c r="B50" s="123"/>
+      <c r="C50" s="114"/>
       <c r="D50" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="E50" s="254"/>
+        <v>102</v>
+      </c>
+      <c r="E50" s="137"/>
       <c r="F50" s="88"/>
       <c r="G50" s="28"/>
       <c r="H50" s="73">
@@ -8244,12 +5255,12 @@
       <c r="AB50" s="19"/>
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B51" s="240"/>
-      <c r="C51" s="238"/>
+      <c r="B51" s="123"/>
+      <c r="C51" s="115"/>
       <c r="D51" s="83" t="s">
-        <v>71</v>
-      </c>
-      <c r="E51" s="255"/>
+        <v>70</v>
+      </c>
+      <c r="E51" s="138"/>
       <c r="F51" s="89"/>
       <c r="G51" s="54"/>
       <c r="H51" s="75">
@@ -8295,17 +5306,17 @@
       <c r="AB51" s="19"/>
     </row>
     <row r="52" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="241"/>
+      <c r="B52" s="124"/>
       <c r="C52" s="32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D52" s="46"/>
       <c r="E52" s="47" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F52" s="92"/>
       <c r="G52" s="48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H52" s="49" t="e">
         <f>H49-H50</f>
@@ -8350,22 +5361,22 @@
     </row>
     <row r="54" spans="2:28" x14ac:dyDescent="0.45">
       <c r="C54" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="2:28" x14ac:dyDescent="0.45">
       <c r="C55" s="18"/>
       <c r="D55" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E55" s="13"/>
       <c r="F55" s="13"/>
       <c r="G55" s="14"/>
       <c r="H55" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I55" s="14"/>
       <c r="J55" s="14"/>
@@ -8380,13 +5391,13 @@
     </row>
     <row r="56" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D56" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="13"/>
       <c r="G56" s="14"/>
       <c r="H56" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I56" s="14"/>
       <c r="J56" s="14"/>
@@ -8401,13 +5412,13 @@
     </row>
     <row r="57" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D57" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E57" s="13"/>
       <c r="F57" s="13"/>
       <c r="G57" s="14"/>
       <c r="H57" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I57" s="14"/>
       <c r="L57" s="14"/>
@@ -8420,13 +5431,13 @@
     </row>
     <row r="58" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D58" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E58" s="13"/>
       <c r="F58" s="13"/>
       <c r="G58" s="14"/>
       <c r="H58" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I58" s="14"/>
       <c r="J58" s="14"/>
@@ -8441,7 +5452,7 @@
     </row>
     <row r="59" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D59" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E59" s="13"/>
       <c r="F59" s="13"/>
@@ -8460,13 +5471,13 @@
     </row>
     <row r="60" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D60" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E60" s="13"/>
       <c r="F60" s="13"/>
       <c r="G60" s="14"/>
       <c r="H60" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I60" s="14"/>
       <c r="J60" s="14"/>
@@ -8481,13 +5492,13 @@
     </row>
     <row r="61" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D61" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E61" s="13"/>
       <c r="F61" s="13"/>
       <c r="G61" s="14"/>
       <c r="H61" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I61" s="14"/>
       <c r="J61" s="14"/>
@@ -8502,13 +5513,13 @@
     </row>
     <row r="62" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D62" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E62" s="13"/>
       <c r="F62" s="13"/>
       <c r="G62" s="14"/>
       <c r="H62" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I62" s="14"/>
       <c r="J62" s="14"/>
@@ -8523,13 +5534,13 @@
     </row>
     <row r="63" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D63" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E63" s="13"/>
       <c r="F63" s="13"/>
       <c r="G63" s="14"/>
       <c r="H63" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I63" s="14"/>
       <c r="J63" s="14"/>
@@ -8544,13 +5555,13 @@
     </row>
     <row r="64" spans="2:28" x14ac:dyDescent="0.45">
       <c r="D64" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E64" s="13"/>
       <c r="F64" s="13"/>
       <c r="G64" s="14"/>
       <c r="H64" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I64" s="14"/>
       <c r="J64" s="14"/>
@@ -8565,13 +5576,13 @@
     </row>
     <row r="65" spans="3:18" x14ac:dyDescent="0.45">
       <c r="D65" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E65" s="13"/>
       <c r="F65" s="13"/>
       <c r="G65" s="14"/>
       <c r="H65" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I65" s="14"/>
       <c r="J65" s="14"/>
@@ -8586,51 +5597,51 @@
     </row>
     <row r="67" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C67" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C68" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E68" s="13"/>
       <c r="F68" s="13"/>
     </row>
     <row r="69" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C69" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E69" s="13"/>
       <c r="F69" s="13"/>
     </row>
     <row r="70" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C70" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E70" s="13"/>
       <c r="F70" s="13"/>
     </row>
     <row r="72" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C72" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C73" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C74" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="3:18" x14ac:dyDescent="0.45">
       <c r="C78" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D78" s="11" t="s">
         <v>68</v>
-      </c>
-      <c r="D78" s="11" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="79" spans="3:18" x14ac:dyDescent="0.45">
@@ -8747,12 +5758,16 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -8766,90 +5781,86 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">
-    <cfRule type="cellIs" dxfId="22" priority="11" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="11" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:Q9">
-    <cfRule type="cellIs" dxfId="21" priority="10" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="10" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:Q10">
-    <cfRule type="cellIs" dxfId="20" priority="12" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="16" priority="12" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:Q11">
-    <cfRule type="cellIs" dxfId="19" priority="14" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="15" priority="14" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:Q13">
-    <cfRule type="cellIs" dxfId="18" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="14" priority="9" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:Q14 H22:Q22 H26:Q26 H30:Q30 H38:Q38 H42:Q42 H46:Q46 H50:Q50">
-    <cfRule type="cellIs" dxfId="17" priority="16" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="13" priority="16" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:Q15 H23:Q23 H31:Q31 H39:Q39 H43:Q43">
-    <cfRule type="cellIs" dxfId="16" priority="18" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="18" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:Q21">
-    <cfRule type="cellIs" dxfId="15" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:Q25">
-    <cfRule type="cellIs" dxfId="14" priority="7" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H27:Q27 H47:Q47 H51:Q51">
-    <cfRule type="cellIs" dxfId="13" priority="15" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="15" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29:Q29">
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37:Q37">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H41:Q41">
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45:Q45">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H49:Q49">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="lessThanOrEqual">
       <formula>3.4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8883,281 +5894,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACF7CB32-E2DC-41F1-851C-45AF01A8E0CE}">
-  <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
-  </sheetPr>
-  <dimension ref="A1:AA9"/>
-  <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="2.59765625" style="104" customWidth="1"/>
-    <col min="2" max="2" width="40.69921875" style="104" customWidth="1"/>
-    <col min="3" max="4" width="13.69921875" style="105" customWidth="1"/>
-    <col min="5" max="15" width="13.69921875" style="104" customWidth="1"/>
-    <col min="16" max="16384" width="8.19921875" style="104"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A1" s="104" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="259" t="s">
-        <v>156</v>
-      </c>
-      <c r="C2" s="260" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="260"/>
-      <c r="E2" s="260"/>
-      <c r="F2" s="262" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="263"/>
-      <c r="H2" s="263"/>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
-      <c r="M2" s="263"/>
-      <c r="N2" s="263"/>
-      <c r="O2" s="264"/>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="B3" s="259"/>
-      <c r="C3" s="260" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" s="260"/>
-      <c r="E3" s="260"/>
-      <c r="F3" s="265"/>
-      <c r="G3" s="266"/>
-      <c r="H3" s="266"/>
-      <c r="I3" s="266"/>
-      <c r="J3" s="266"/>
-      <c r="K3" s="266"/>
-      <c r="L3" s="266"/>
-      <c r="M3" s="266"/>
-      <c r="N3" s="266"/>
-      <c r="O3" s="267"/>
-    </row>
-    <row r="4" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="259"/>
-      <c r="C4" s="107" t="s">
-        <v>141</v>
-      </c>
-      <c r="D4" s="107" t="s">
-        <v>149</v>
-      </c>
-      <c r="E4" s="106" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="97" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="97" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="97" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" s="97" t="s">
-        <v>140</v>
-      </c>
-      <c r="J4" s="97" t="s">
-        <v>61</v>
-      </c>
-      <c r="K4" s="97" t="s">
-        <v>62</v>
-      </c>
-      <c r="L4" s="97" t="s">
-        <v>63</v>
-      </c>
-      <c r="M4" s="97" t="s">
-        <v>64</v>
-      </c>
-      <c r="N4" s="97" t="s">
-        <v>65</v>
-      </c>
-      <c r="O4" s="97" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="B5" s="108" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="109"/>
-      <c r="J5" s="109"/>
-      <c r="K5" s="109"/>
-      <c r="L5" s="109"/>
-      <c r="M5" s="109"/>
-      <c r="N5" s="109"/>
-      <c r="O5" s="109"/>
-      <c r="Q5" s="111"/>
-    </row>
-    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="261" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="112"/>
-      <c r="D6" s="112"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="112"/>
-      <c r="H6" s="112"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="112"/>
-      <c r="L6" s="112"/>
-      <c r="M6" s="112"/>
-      <c r="N6" s="112"/>
-      <c r="O6" s="114"/>
-    </row>
-    <row r="7" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="229"/>
-      <c r="C7" s="115"/>
-      <c r="D7" s="115"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="117"/>
-      <c r="J7" s="117"/>
-      <c r="K7" s="117"/>
-      <c r="L7" s="117"/>
-      <c r="M7" s="117"/>
-      <c r="N7" s="117"/>
-      <c r="O7" s="117"/>
-      <c r="P7" s="118"/>
-      <c r="Q7" s="118"/>
-      <c r="R7" s="118"/>
-      <c r="S7" s="118"/>
-      <c r="T7" s="118"/>
-      <c r="U7" s="118"/>
-      <c r="V7" s="118"/>
-      <c r="W7" s="118"/>
-      <c r="X7" s="118"/>
-      <c r="Y7" s="118"/>
-      <c r="Z7" s="118"/>
-      <c r="AA7" s="118"/>
-    </row>
-    <row r="8" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="217"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="121"/>
-      <c r="K8" s="121"/>
-      <c r="L8" s="121"/>
-      <c r="M8" s="121"/>
-      <c r="N8" s="121"/>
-      <c r="O8" s="122"/>
-      <c r="P8" s="118"/>
-      <c r="Q8" s="118"/>
-      <c r="R8" s="118"/>
-      <c r="S8" s="118"/>
-      <c r="T8" s="118"/>
-      <c r="U8" s="118"/>
-      <c r="V8" s="118"/>
-      <c r="W8" s="118"/>
-      <c r="X8" s="118"/>
-      <c r="Y8" s="118"/>
-      <c r="Z8" s="118"/>
-      <c r="AA8" s="118"/>
-    </row>
-    <row r="9" spans="1:27" ht="18.600000000000001" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="123" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="124" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="124"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="127"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="127"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="127"/>
-      <c r="L9" s="126"/>
-      <c r="M9" s="127"/>
-      <c r="N9" s="126"/>
-      <c r="O9" s="128"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="F2:O3"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="C5:E5">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:O6">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:O7">
-    <cfRule type="cellIs" dxfId="5" priority="13" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:O8">
-    <cfRule type="cellIs" dxfId="4" priority="14" operator="lessThanOrEqual">
-      <formula>3.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="31" id="{929A1E3A-38D3-44BC-9132-468325377686}">
-            <x14:iconSet iconSet="3Arrows" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>-0.25</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0.25</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>F9:N9</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86286144-F6F8-4142-BAA1-C8861DBF28F2}">
   <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
@@ -9171,7 +5908,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="94" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -9196,84 +5933,84 @@
       <c r="E2" s="95"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="F3" s="197" t="s">
-        <v>206</v>
-      </c>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="198"/>
-      <c r="O3" s="199"/>
+      <c r="F3" s="106" t="s">
+        <v>198</v>
+      </c>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
+      <c r="O3" s="108"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" s="93" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="93" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="93" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="93" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="93" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" s="97" t="s">
+        <v>155</v>
+      </c>
+      <c r="G4" s="97" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4" s="97" t="s">
         <v>157</v>
       </c>
-      <c r="B4" s="93" t="s">
+      <c r="I4" s="97" t="s">
+        <v>158</v>
+      </c>
+      <c r="J4" s="97" t="s">
+        <v>159</v>
+      </c>
+      <c r="K4" s="97" t="s">
+        <v>160</v>
+      </c>
+      <c r="L4" s="97" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="93" t="s">
-        <v>158</v>
-      </c>
-      <c r="D4" s="93" t="s">
-        <v>159</v>
-      </c>
-      <c r="E4" s="93" t="s">
-        <v>160</v>
-      </c>
-      <c r="F4" s="97" t="s">
+      <c r="M4" s="97" t="s">
+        <v>162</v>
+      </c>
+      <c r="N4" s="97" t="s">
         <v>163</v>
       </c>
-      <c r="G4" s="97" t="s">
+      <c r="O4" s="97" t="s">
         <v>164</v>
-      </c>
-      <c r="H4" s="97" t="s">
-        <v>165</v>
-      </c>
-      <c r="I4" s="97" t="s">
-        <v>166</v>
-      </c>
-      <c r="J4" s="97" t="s">
-        <v>167</v>
-      </c>
-      <c r="K4" s="97" t="s">
-        <v>168</v>
-      </c>
-      <c r="L4" s="97" t="s">
-        <v>169</v>
-      </c>
-      <c r="M4" s="97" t="s">
-        <v>170</v>
-      </c>
-      <c r="N4" s="97" t="s">
-        <v>171</v>
-      </c>
-      <c r="O4" s="97" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" s="98" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B5" s="98"/>
       <c r="C5" s="98"/>
       <c r="D5" s="98"/>
       <c r="E5" s="98"/>
-      <c r="F5" s="203"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="203"/>
-      <c r="I5" s="203"/>
-      <c r="J5" s="203"/>
-      <c r="K5" s="203"/>
-      <c r="L5" s="203"/>
-      <c r="M5" s="203"/>
-      <c r="N5" s="203"/>
-      <c r="O5" s="203"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="112"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="112"/>
+      <c r="M5" s="112"/>
+      <c r="N5" s="112"/>
+      <c r="O5" s="112"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -9287,18 +6024,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D283FD5-20E4-4A5F-8CE0-6E0AB2CC1AD7}">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="40.69921875" style="195" customWidth="1"/>
+    <col min="1" max="1" width="40.69921875" style="104" customWidth="1"/>
     <col min="2" max="13" width="14.69921875" style="96" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="94" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -9317,79 +6054,79 @@
       <c r="A2" s="94"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="196"/>
-      <c r="B3" s="197" t="s">
-        <v>206</v>
-      </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
-      <c r="L3" s="198"/>
-      <c r="M3" s="199"/>
+      <c r="A3" s="105"/>
+      <c r="B3" s="106" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="108"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" s="93" t="s">
-        <v>205</v>
-      </c>
-      <c r="B4" s="201" t="s">
-        <v>209</v>
-      </c>
-      <c r="C4" s="201" t="s">
-        <v>210</v>
+        <v>197</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="110" t="s">
+        <v>202</v>
       </c>
       <c r="D4" s="97" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="97" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" s="97" t="s">
+        <v>157</v>
+      </c>
+      <c r="G4" s="97" t="s">
+        <v>158</v>
+      </c>
+      <c r="H4" s="97" t="s">
+        <v>159</v>
+      </c>
+      <c r="I4" s="97" t="s">
+        <v>160</v>
+      </c>
+      <c r="J4" s="97" t="s">
+        <v>161</v>
+      </c>
+      <c r="K4" s="97" t="s">
+        <v>162</v>
+      </c>
+      <c r="L4" s="97" t="s">
         <v>163</v>
       </c>
-      <c r="E4" s="97" t="s">
+      <c r="M4" s="97" t="s">
         <v>164</v>
       </c>
-      <c r="F4" s="97" t="s">
-        <v>165</v>
-      </c>
-      <c r="G4" s="97" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" s="97" t="s">
-        <v>167</v>
-      </c>
-      <c r="I4" s="97" t="s">
-        <v>168</v>
-      </c>
-      <c r="J4" s="97" t="s">
-        <v>169</v>
-      </c>
-      <c r="K4" s="97" t="s">
-        <v>170</v>
-      </c>
-      <c r="L4" s="97" t="s">
-        <v>171</v>
-      </c>
-      <c r="M4" s="97" t="s">
-        <v>172</v>
-      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="200" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="202"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="203"/>
-      <c r="E5" s="203"/>
-      <c r="F5" s="203"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="203"/>
-      <c r="I5" s="203"/>
-      <c r="J5" s="203"/>
-      <c r="K5" s="203"/>
-      <c r="L5" s="203"/>
-      <c r="M5" s="203"/>
+      <c r="A5" s="109" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="112"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="112"/>
+      <c r="M5" s="112"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -9403,18 +6140,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20657923-2F38-4DA8-AAA7-2504A3495A9C}">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="40.69921875" style="195" customWidth="1"/>
+    <col min="1" max="1" width="40.69921875" style="104" customWidth="1"/>
     <col min="2" max="13" width="14.69921875" style="96" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="94" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -9433,79 +6170,79 @@
       <c r="A2" s="94"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="196"/>
-      <c r="B3" s="197" t="s">
-        <v>206</v>
-      </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
-      <c r="L3" s="198"/>
-      <c r="M3" s="199"/>
+      <c r="A3" s="105"/>
+      <c r="B3" s="106" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="108"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" s="93" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="110" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="97" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="97" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" s="97" t="s">
+        <v>157</v>
+      </c>
+      <c r="G4" s="97" t="s">
+        <v>158</v>
+      </c>
+      <c r="H4" s="97" t="s">
         <v>159</v>
       </c>
-      <c r="B4" s="201" t="s">
-        <v>209</v>
-      </c>
-      <c r="C4" s="201" t="s">
-        <v>210</v>
-      </c>
-      <c r="D4" s="97" t="s">
+      <c r="I4" s="97" t="s">
+        <v>160</v>
+      </c>
+      <c r="J4" s="97" t="s">
+        <v>161</v>
+      </c>
+      <c r="K4" s="97" t="s">
+        <v>162</v>
+      </c>
+      <c r="L4" s="97" t="s">
         <v>163</v>
       </c>
-      <c r="E4" s="97" t="s">
+      <c r="M4" s="97" t="s">
         <v>164</v>
       </c>
-      <c r="F4" s="97" t="s">
-        <v>165</v>
-      </c>
-      <c r="G4" s="97" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" s="97" t="s">
-        <v>167</v>
-      </c>
-      <c r="I4" s="97" t="s">
-        <v>168</v>
-      </c>
-      <c r="J4" s="97" t="s">
-        <v>169</v>
-      </c>
-      <c r="K4" s="97" t="s">
-        <v>170</v>
-      </c>
-      <c r="L4" s="97" t="s">
-        <v>171</v>
-      </c>
-      <c r="M4" s="97" t="s">
-        <v>172</v>
-      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="200" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="202"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="203"/>
-      <c r="E5" s="203"/>
-      <c r="F5" s="203"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="203"/>
-      <c r="I5" s="203"/>
-      <c r="J5" s="203"/>
-      <c r="K5" s="203"/>
-      <c r="L5" s="203"/>
-      <c r="M5" s="203"/>
+      <c r="A5" s="109" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="112"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="112"/>
+      <c r="M5" s="112"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -9519,18 +6256,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A3F122-A8D4-4240-B606-D85C64EBC3DE}">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="40.69921875" style="195" customWidth="1"/>
+    <col min="1" max="1" width="40.69921875" style="104" customWidth="1"/>
     <col min="2" max="13" width="14.69921875" style="96" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="94" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -9549,79 +6286,79 @@
       <c r="A2" s="94"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="196"/>
-      <c r="B3" s="197" t="s">
-        <v>206</v>
-      </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
-      <c r="L3" s="198"/>
-      <c r="M3" s="199"/>
+      <c r="A3" s="105"/>
+      <c r="B3" s="106" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="108"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" s="93" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="110" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="97" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="97" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" s="97" t="s">
+        <v>157</v>
+      </c>
+      <c r="G4" s="97" t="s">
+        <v>158</v>
+      </c>
+      <c r="H4" s="97" t="s">
+        <v>159</v>
+      </c>
+      <c r="I4" s="97" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="201" t="s">
-        <v>209</v>
-      </c>
-      <c r="C4" s="201" t="s">
-        <v>210</v>
-      </c>
-      <c r="D4" s="97" t="s">
+      <c r="J4" s="97" t="s">
+        <v>161</v>
+      </c>
+      <c r="K4" s="97" t="s">
+        <v>162</v>
+      </c>
+      <c r="L4" s="97" t="s">
         <v>163</v>
       </c>
-      <c r="E4" s="97" t="s">
+      <c r="M4" s="97" t="s">
         <v>164</v>
       </c>
-      <c r="F4" s="97" t="s">
-        <v>165</v>
-      </c>
-      <c r="G4" s="97" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" s="97" t="s">
-        <v>167</v>
-      </c>
-      <c r="I4" s="97" t="s">
-        <v>168</v>
-      </c>
-      <c r="J4" s="97" t="s">
-        <v>169</v>
-      </c>
-      <c r="K4" s="97" t="s">
-        <v>170</v>
-      </c>
-      <c r="L4" s="97" t="s">
-        <v>171</v>
-      </c>
-      <c r="M4" s="97" t="s">
-        <v>172</v>
-      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="200" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="202"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="203"/>
-      <c r="E5" s="203"/>
-      <c r="F5" s="203"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="203"/>
-      <c r="I5" s="203"/>
-      <c r="J5" s="203"/>
-      <c r="K5" s="203"/>
-      <c r="L5" s="203"/>
-      <c r="M5" s="203"/>
+      <c r="A5" s="109" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="112"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="112"/>
+      <c r="M5" s="112"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -9635,7 +6372,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{641A4A2E-373C-41E1-A3D4-3CA1E92913A7}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
@@ -9671,7 +6408,7 @@
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.45">
       <c r="A1" s="94" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -9705,144 +6442,144 @@
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.45">
       <c r="A3" s="93" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="93" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="93" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="93" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="93" t="s">
+        <v>152</v>
+      </c>
+      <c r="F3" s="93" t="s">
+        <v>165</v>
+      </c>
+      <c r="G3" s="97" t="s">
+        <v>155</v>
+      </c>
+      <c r="H3" s="97" t="s">
+        <v>156</v>
+      </c>
+      <c r="I3" s="97" t="s">
         <v>157</v>
       </c>
-      <c r="B3" s="93" t="s">
+      <c r="J3" s="97" t="s">
+        <v>158</v>
+      </c>
+      <c r="K3" s="97" t="s">
+        <v>159</v>
+      </c>
+      <c r="L3" s="97" t="s">
+        <v>160</v>
+      </c>
+      <c r="M3" s="97" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="93" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" s="93" t="s">
-        <v>159</v>
-      </c>
-      <c r="E3" s="93" t="s">
-        <v>160</v>
-      </c>
-      <c r="F3" s="93" t="s">
+      <c r="N3" s="97" t="s">
+        <v>162</v>
+      </c>
+      <c r="O3" s="97" t="s">
+        <v>163</v>
+      </c>
+      <c r="P3" s="97" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q3" s="102" t="s">
+        <v>166</v>
+      </c>
+      <c r="R3" s="102" t="s">
+        <v>167</v>
+      </c>
+      <c r="S3" s="102" t="s">
+        <v>168</v>
+      </c>
+      <c r="T3" s="102" t="s">
+        <v>169</v>
+      </c>
+      <c r="U3" s="102" t="s">
+        <v>170</v>
+      </c>
+      <c r="V3" s="102" t="s">
+        <v>171</v>
+      </c>
+      <c r="W3" s="102" t="s">
+        <v>172</v>
+      </c>
+      <c r="X3" s="102" t="s">
         <v>173</v>
       </c>
-      <c r="G3" s="97" t="s">
-        <v>163</v>
-      </c>
-      <c r="H3" s="97" t="s">
-        <v>164</v>
-      </c>
-      <c r="I3" s="97" t="s">
-        <v>165</v>
-      </c>
-      <c r="J3" s="97" t="s">
-        <v>166</v>
-      </c>
-      <c r="K3" s="97" t="s">
-        <v>167</v>
-      </c>
-      <c r="L3" s="97" t="s">
-        <v>168</v>
-      </c>
-      <c r="M3" s="97" t="s">
-        <v>169</v>
-      </c>
-      <c r="N3" s="97" t="s">
-        <v>170</v>
-      </c>
-      <c r="O3" s="97" t="s">
-        <v>171</v>
-      </c>
-      <c r="P3" s="97" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q3" s="102" t="s">
+      <c r="Y3" s="102" t="s">
         <v>174</v>
       </c>
-      <c r="R3" s="102" t="s">
+      <c r="Z3" s="102" t="s">
         <v>175</v>
       </c>
-      <c r="S3" s="102" t="s">
+      <c r="AA3" s="102" t="s">
         <v>176</v>
       </c>
-      <c r="T3" s="102" t="s">
+      <c r="AB3" s="102" t="s">
         <v>177</v>
       </c>
-      <c r="U3" s="102" t="s">
+      <c r="AC3" s="102" t="s">
         <v>178</v>
       </c>
-      <c r="V3" s="102" t="s">
+      <c r="AD3" s="102" t="s">
         <v>179</v>
       </c>
-      <c r="W3" s="102" t="s">
+      <c r="AE3" s="102" t="s">
         <v>180</v>
       </c>
-      <c r="X3" s="102" t="s">
+      <c r="AF3" s="102" t="s">
         <v>181</v>
       </c>
-      <c r="Y3" s="102" t="s">
+      <c r="AG3" s="102" t="s">
         <v>182</v>
       </c>
-      <c r="Z3" s="102" t="s">
+      <c r="AH3" s="102" t="s">
         <v>183</v>
       </c>
-      <c r="AA3" s="102" t="s">
+      <c r="AI3" s="102" t="s">
         <v>184</v>
       </c>
-      <c r="AB3" s="102" t="s">
+      <c r="AJ3" s="102" t="s">
         <v>185</v>
       </c>
-      <c r="AC3" s="102" t="s">
+      <c r="AK3" s="102" t="s">
         <v>186</v>
       </c>
-      <c r="AD3" s="102" t="s">
+      <c r="AL3" s="102" t="s">
         <v>187</v>
       </c>
-      <c r="AE3" s="102" t="s">
+      <c r="AM3" s="102" t="s">
         <v>188</v>
       </c>
-      <c r="AF3" s="102" t="s">
+      <c r="AN3" s="102" t="s">
         <v>189</v>
       </c>
-      <c r="AG3" s="102" t="s">
+      <c r="AO3" s="102" t="s">
         <v>190</v>
       </c>
-      <c r="AH3" s="102" t="s">
+      <c r="AP3" s="102" t="s">
         <v>191</v>
       </c>
-      <c r="AI3" s="102" t="s">
+      <c r="AQ3" s="102" t="s">
         <v>192</v>
       </c>
-      <c r="AJ3" s="102" t="s">
+      <c r="AR3" s="102" t="s">
         <v>193</v>
       </c>
-      <c r="AK3" s="102" t="s">
+      <c r="AS3" s="102" t="s">
         <v>194</v>
-      </c>
-      <c r="AL3" s="102" t="s">
-        <v>195</v>
-      </c>
-      <c r="AM3" s="102" t="s">
-        <v>196</v>
-      </c>
-      <c r="AN3" s="102" t="s">
-        <v>197</v>
-      </c>
-      <c r="AO3" s="102" t="s">
-        <v>198</v>
-      </c>
-      <c r="AP3" s="102" t="s">
-        <v>199</v>
-      </c>
-      <c r="AQ3" s="102" t="s">
-        <v>200</v>
-      </c>
-      <c r="AR3" s="102" t="s">
-        <v>201</v>
-      </c>
-      <c r="AS3" s="102" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.45">
       <c r="A4" s="98" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B4" s="98"/>
       <c r="C4" s="98"/>
@@ -9896,7 +6633,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
@@ -9918,7 +6655,7 @@
         <v>46</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>47</v>
@@ -9983,7 +6720,7 @@
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.45">
       <c r="M3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:34" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -10001,7 +6738,7 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>3</v>
@@ -10244,91 +6981,91 @@
         <v>43</v>
       </c>
       <c r="F8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" t="s">
         <v>104</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>105</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>106</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>107</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>108</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>109</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>110</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
+        <v>130</v>
+      </c>
+      <c r="O8" t="s">
         <v>111</v>
       </c>
-      <c r="N8" t="s">
+      <c r="P8" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>113</v>
+      </c>
+      <c r="R8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S8" t="s">
+        <v>115</v>
+      </c>
+      <c r="T8" t="s">
+        <v>116</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W8" t="s">
+        <v>119</v>
+      </c>
+      <c r="X8" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG8" t="s">
         <v>131</v>
       </c>
-      <c r="O8" t="s">
-        <v>112</v>
-      </c>
-      <c r="P8" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>114</v>
-      </c>
-      <c r="R8" t="s">
-        <v>115</v>
-      </c>
-      <c r="S8" t="s">
-        <v>116</v>
-      </c>
-      <c r="T8" t="s">
-        <v>117</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="V8" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="W8" t="s">
-        <v>120</v>
-      </c>
-      <c r="X8" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>124</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>126</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>127</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>128</v>
-      </c>
-      <c r="AF8" t="s">
+      <c r="AH8" t="s">
         <v>129</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>132</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.45">

--- a/tool/track-aggregator/template/アンケート結果.xlsx
+++ b/tool/track-aggregator/template/アンケート結果.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\track-aggregator\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\track-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4871105E-0667-4D55-937D-CA93A376B4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5713FA71-80C7-47BD-9A49-EE265AB35086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="経年比較（前年同じFMT）" sheetId="22" state="hidden" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'経年比較（前年同じFMT）'!$B$2:$Q$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'詳細-ユーザ別'!$A$3:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'詳細-ユーザ別'!$A$3:$O$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="202">
   <si>
     <t>目的達成</t>
     <rPh sb="0" eb="2">
@@ -968,10 +968,6 @@
   <si>
     <t>学習環境</t>
     <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>DM</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>質問1</t>
@@ -2295,6 +2291,24 @@
     <xf numFmtId="179" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2303,24 +2317,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -2855,10 +2851,10 @@
   <sheetData>
     <row r="1" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="113" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="117"/>
+      <c r="C2" s="114"/>
       <c r="D2" s="125" t="s">
         <v>54</v>
       </c>
@@ -2881,8 +2877,8 @@
       <c r="Q2" s="129"/>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="B3" s="118"/>
-      <c r="C3" s="119"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="116"/>
       <c r="D3" s="126"/>
       <c r="E3" s="130" t="s">
         <v>96</v>
@@ -2901,8 +2897,8 @@
       <c r="Q3" s="20"/>
     </row>
     <row r="4" spans="2:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="120"/>
-      <c r="C4" s="121"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="118"/>
       <c r="D4" s="126"/>
       <c r="E4" s="85" t="s">
         <v>140</v>
@@ -2948,7 +2944,7 @@
       <c r="B5" s="122" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="113" t="s">
+      <c r="C5" s="119" t="s">
         <v>137</v>
       </c>
       <c r="D5" s="33" t="s">
@@ -3003,7 +2999,7 @@
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B6" s="123"/>
-      <c r="C6" s="114"/>
+      <c r="C6" s="120"/>
       <c r="D6" s="26" t="s">
         <v>102</v>
       </c>
@@ -3057,7 +3053,7 @@
     </row>
     <row r="7" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B7" s="123"/>
-      <c r="C7" s="115"/>
+      <c r="C7" s="121"/>
       <c r="D7" s="83" t="s">
         <v>70</v>
       </c>
@@ -3163,7 +3159,7 @@
     </row>
     <row r="9" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B9" s="123"/>
-      <c r="C9" s="113" t="s">
+      <c r="C9" s="119" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -3215,7 +3211,7 @@
     </row>
     <row r="10" spans="2:29" hidden="1" x14ac:dyDescent="0.45">
       <c r="B10" s="123"/>
-      <c r="C10" s="114"/>
+      <c r="C10" s="120"/>
       <c r="D10" s="26" t="s">
         <v>102</v>
       </c>
@@ -3267,7 +3263,7 @@
     </row>
     <row r="11" spans="2:29" ht="15.6" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="123"/>
-      <c r="C11" s="115"/>
+      <c r="C11" s="121"/>
       <c r="D11" s="34" t="s">
         <v>70</v>
       </c>
@@ -3373,7 +3369,7 @@
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B13" s="123"/>
-      <c r="C13" s="113" t="s">
+      <c r="C13" s="119" t="s">
         <v>142</v>
       </c>
       <c r="D13" s="33" t="s">
@@ -3425,7 +3421,7 @@
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B14" s="123"/>
-      <c r="C14" s="114"/>
+      <c r="C14" s="120"/>
       <c r="D14" s="26" t="s">
         <v>102</v>
       </c>
@@ -3477,7 +3473,7 @@
     </row>
     <row r="15" spans="2:29" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B15" s="123"/>
-      <c r="C15" s="115"/>
+      <c r="C15" s="121"/>
       <c r="D15" s="83" t="s">
         <v>70</v>
       </c>
@@ -3594,10 +3590,10 @@
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="116" t="s">
+      <c r="B18" s="113" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="117"/>
+      <c r="C18" s="114"/>
       <c r="D18" s="125" t="s">
         <v>54</v>
       </c>
@@ -3620,8 +3616,8 @@
       <c r="Q18" s="141"/>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="118"/>
-      <c r="C19" s="119"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="116"/>
       <c r="D19" s="126"/>
       <c r="E19" s="130" t="s">
         <v>96</v>
@@ -3640,8 +3636,8 @@
       <c r="Q19" s="69"/>
     </row>
     <row r="20" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="120"/>
-      <c r="C20" s="121"/>
+      <c r="B20" s="117"/>
+      <c r="C20" s="118"/>
       <c r="D20" s="126"/>
       <c r="E20" s="85" t="s">
         <v>140</v>
@@ -3687,7 +3683,7 @@
       <c r="B21" s="122" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="113" t="s">
+      <c r="C21" s="119" t="s">
         <v>99</v>
       </c>
       <c r="D21" s="33" t="s">
@@ -3748,7 +3744,7 @@
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B22" s="123"/>
-      <c r="C22" s="114"/>
+      <c r="C22" s="120"/>
       <c r="D22" s="26" t="s">
         <v>102</v>
       </c>
@@ -3803,7 +3799,7 @@
     </row>
     <row r="23" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B23" s="123"/>
-      <c r="C23" s="115"/>
+      <c r="C23" s="121"/>
       <c r="D23" s="83" t="s">
         <v>70</v>
       </c>
@@ -3914,7 +3910,7 @@
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B25" s="123"/>
-      <c r="C25" s="113" t="s">
+      <c r="C25" s="119" t="s">
         <v>98</v>
       </c>
       <c r="D25" s="33" t="s">
@@ -3975,7 +3971,7 @@
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B26" s="123"/>
-      <c r="C26" s="114"/>
+      <c r="C26" s="120"/>
       <c r="D26" s="26" t="s">
         <v>102</v>
       </c>
@@ -4030,7 +4026,7 @@
     </row>
     <row r="27" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B27" s="123"/>
-      <c r="C27" s="115"/>
+      <c r="C27" s="121"/>
       <c r="D27" s="83" t="s">
         <v>70</v>
       </c>
@@ -4141,7 +4137,7 @@
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B29" s="123"/>
-      <c r="C29" s="113" t="s">
+      <c r="C29" s="119" t="s">
         <v>97</v>
       </c>
       <c r="D29" s="33" t="s">
@@ -4202,7 +4198,7 @@
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B30" s="123"/>
-      <c r="C30" s="114"/>
+      <c r="C30" s="120"/>
       <c r="D30" s="26" t="s">
         <v>102</v>
       </c>
@@ -4257,7 +4253,7 @@
     </row>
     <row r="31" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B31" s="123"/>
-      <c r="C31" s="115"/>
+      <c r="C31" s="121"/>
       <c r="D31" s="83" t="s">
         <v>70</v>
       </c>
@@ -4379,10 +4375,10 @@
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B34" s="116" t="s">
+      <c r="B34" s="113" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="117"/>
+      <c r="C34" s="114"/>
       <c r="D34" s="125" t="s">
         <v>54</v>
       </c>
@@ -4405,8 +4401,8 @@
       <c r="Q34" s="141"/>
     </row>
     <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="118"/>
-      <c r="C35" s="119"/>
+      <c r="B35" s="115"/>
+      <c r="C35" s="116"/>
       <c r="D35" s="126"/>
       <c r="E35" s="130" t="s">
         <v>96</v>
@@ -4425,8 +4421,8 @@
       <c r="Q35" s="69"/>
     </row>
     <row r="36" spans="2:28" ht="30.6" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="120"/>
-      <c r="C36" s="121"/>
+      <c r="B36" s="117"/>
+      <c r="C36" s="118"/>
       <c r="D36" s="126"/>
       <c r="E36" s="85" t="s">
         <v>140</v>
@@ -4472,7 +4468,7 @@
       <c r="B37" s="122" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="113" t="s">
+      <c r="C37" s="119" t="s">
         <v>94</v>
       </c>
       <c r="D37" s="33" t="s">
@@ -4533,7 +4529,7 @@
     </row>
     <row r="38" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B38" s="123"/>
-      <c r="C38" s="114"/>
+      <c r="C38" s="120"/>
       <c r="D38" s="26" t="s">
         <v>102</v>
       </c>
@@ -4588,7 +4584,7 @@
     </row>
     <row r="39" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B39" s="123"/>
-      <c r="C39" s="115"/>
+      <c r="C39" s="121"/>
       <c r="D39" s="83" t="s">
         <v>70</v>
       </c>
@@ -4699,7 +4695,7 @@
     </row>
     <row r="41" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B41" s="123"/>
-      <c r="C41" s="113" t="s">
+      <c r="C41" s="119" t="s">
         <v>79</v>
       </c>
       <c r="D41" s="33" t="s">
@@ -4760,7 +4756,7 @@
     </row>
     <row r="42" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B42" s="123"/>
-      <c r="C42" s="114"/>
+      <c r="C42" s="120"/>
       <c r="D42" s="26" t="s">
         <v>102</v>
       </c>
@@ -4815,7 +4811,7 @@
     </row>
     <row r="43" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B43" s="123"/>
-      <c r="C43" s="115"/>
+      <c r="C43" s="121"/>
       <c r="D43" s="83" t="s">
         <v>70</v>
       </c>
@@ -4926,7 +4922,7 @@
     </row>
     <row r="45" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B45" s="123"/>
-      <c r="C45" s="113" t="s">
+      <c r="C45" s="119" t="s">
         <v>93</v>
       </c>
       <c r="D45" s="33" t="s">
@@ -4987,7 +4983,7 @@
     </row>
     <row r="46" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B46" s="123"/>
-      <c r="C46" s="114"/>
+      <c r="C46" s="120"/>
       <c r="D46" s="26" t="s">
         <v>102</v>
       </c>
@@ -5042,7 +5038,7 @@
     </row>
     <row r="47" spans="2:28" ht="15.6" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B47" s="123"/>
-      <c r="C47" s="115"/>
+      <c r="C47" s="121"/>
       <c r="D47" s="83" t="s">
         <v>70</v>
       </c>
@@ -5153,7 +5149,7 @@
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.45">
       <c r="B49" s="123"/>
-      <c r="C49" s="113" t="s">
+      <c r="C49" s="119" t="s">
         <v>92</v>
       </c>
       <c r="D49" s="33" t="s">
@@ -5205,7 +5201,7 @@
     </row>
     <row r="50" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="123"/>
-      <c r="C50" s="114"/>
+      <c r="C50" s="120"/>
       <c r="D50" s="26" t="s">
         <v>102</v>
       </c>
@@ -5256,7 +5252,7 @@
     </row>
     <row r="51" spans="2:28" ht="18.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B51" s="123"/>
-      <c r="C51" s="115"/>
+      <c r="C51" s="121"/>
       <c r="D51" s="83" t="s">
         <v>70</v>
       </c>
@@ -5758,16 +5754,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:C4"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="B5:B16"/>
-    <mergeCell ref="B21:B32"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B34:C36"/>
+    <mergeCell ref="B37:B52"/>
+    <mergeCell ref="C37:C39"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="H2:Q2"/>
     <mergeCell ref="E3:G3"/>
@@ -5781,12 +5773,16 @@
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B34:C36"/>
-    <mergeCell ref="B37:B52"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B2:C4"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B21:B32"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C25:C27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H5:Q7">
@@ -5908,7 +5904,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="94" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -5934,7 +5930,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="F3" s="106" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3" s="107"/>
       <c r="H3" s="107"/>
@@ -6035,7 +6031,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="94" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -6056,7 +6052,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" s="105"/>
       <c r="B3" s="106" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C3" s="107"/>
       <c r="D3" s="107"/>
@@ -6072,13 +6068,13 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" s="93" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B4" s="110" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" s="110" t="s">
         <v>201</v>
-      </c>
-      <c r="C4" s="110" t="s">
-        <v>202</v>
       </c>
       <c r="D4" s="97" t="s">
         <v>155</v>
@@ -6151,7 +6147,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="94" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -6172,7 +6168,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" s="105"/>
       <c r="B3" s="106" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C3" s="107"/>
       <c r="D3" s="107"/>
@@ -6191,10 +6187,10 @@
         <v>151</v>
       </c>
       <c r="B4" s="110" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" s="110" t="s">
         <v>201</v>
-      </c>
-      <c r="C4" s="110" t="s">
-        <v>202</v>
       </c>
       <c r="D4" s="97" t="s">
         <v>155</v>
@@ -6267,7 +6263,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="94" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -6288,7 +6284,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" s="105"/>
       <c r="B3" s="106" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C3" s="107"/>
       <c r="D3" s="107"/>
@@ -6307,10 +6303,10 @@
         <v>152</v>
       </c>
       <c r="B4" s="110" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" s="110" t="s">
         <v>201</v>
-      </c>
-      <c r="C4" s="110" t="s">
-        <v>202</v>
       </c>
       <c r="D4" s="97" t="s">
         <v>155</v>
@@ -6377,38 +6373,37 @@
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:AT4"/>
+  <dimension ref="A1:AS4"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelCol="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19.296875" style="100" customWidth="1"/>
     <col min="2" max="2" width="30.69921875" style="100" customWidth="1"/>
     <col min="3" max="3" width="40.69921875" style="100" customWidth="1"/>
     <col min="4" max="5" width="15.69921875" style="100" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" style="100" customWidth="1"/>
-    <col min="7" max="16" width="14.69921875" style="96" customWidth="1"/>
-    <col min="17" max="19" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="27" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="28" max="29" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="30" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="31" max="32" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="33" max="33" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="34" max="35" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="36" max="36" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="37" max="38" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="39" max="39" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="40" max="41" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="42" max="42" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="43" max="43" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="44" max="44" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="45" max="45" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="46" max="46" width="8.796875" style="96" collapsed="1"/>
-    <col min="47" max="16384" width="8.796875" style="96"/>
+    <col min="6" max="15" width="14.69921875" style="96" customWidth="1"/>
+    <col min="16" max="18" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="26" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="27" max="28" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="29" max="29" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="31" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="32" max="32" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="34" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="35" max="35" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="36" max="37" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="38" max="38" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="39" max="40" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="41" max="41" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="42" max="42" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="43" max="43" width="13.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="44" max="44" width="50.69921875" style="96" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="45" max="45" width="8.796875" style="96" collapsed="1"/>
+    <col min="46" max="16384" width="8.796875" style="96"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A1" s="94" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -6430,17 +6425,15 @@
       <c r="S1" s="95"/>
       <c r="T1" s="95"/>
       <c r="U1" s="95"/>
-      <c r="V1" s="95"/>
-    </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A2" s="95"/>
       <c r="B2" s="95"/>
       <c r="C2" s="95"/>
       <c r="D2" s="95"/>
       <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-    </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A3" s="93" t="s">
         <v>149</v>
       </c>
@@ -6456,38 +6449,38 @@
       <c r="E3" s="93" t="s">
         <v>152</v>
       </c>
-      <c r="F3" s="93" t="s">
+      <c r="F3" s="97" t="s">
+        <v>155</v>
+      </c>
+      <c r="G3" s="97" t="s">
+        <v>156</v>
+      </c>
+      <c r="H3" s="97" t="s">
+        <v>157</v>
+      </c>
+      <c r="I3" s="97" t="s">
+        <v>158</v>
+      </c>
+      <c r="J3" s="97" t="s">
+        <v>159</v>
+      </c>
+      <c r="K3" s="97" t="s">
+        <v>160</v>
+      </c>
+      <c r="L3" s="97" t="s">
+        <v>161</v>
+      </c>
+      <c r="M3" s="97" t="s">
+        <v>162</v>
+      </c>
+      <c r="N3" s="97" t="s">
+        <v>163</v>
+      </c>
+      <c r="O3" s="97" t="s">
+        <v>164</v>
+      </c>
+      <c r="P3" s="102" t="s">
         <v>165</v>
-      </c>
-      <c r="G3" s="97" t="s">
-        <v>155</v>
-      </c>
-      <c r="H3" s="97" t="s">
-        <v>156</v>
-      </c>
-      <c r="I3" s="97" t="s">
-        <v>157</v>
-      </c>
-      <c r="J3" s="97" t="s">
-        <v>158</v>
-      </c>
-      <c r="K3" s="97" t="s">
-        <v>159</v>
-      </c>
-      <c r="L3" s="97" t="s">
-        <v>160</v>
-      </c>
-      <c r="M3" s="97" t="s">
-        <v>161</v>
-      </c>
-      <c r="N3" s="97" t="s">
-        <v>162</v>
-      </c>
-      <c r="O3" s="97" t="s">
-        <v>163</v>
-      </c>
-      <c r="P3" s="97" t="s">
-        <v>164</v>
       </c>
       <c r="Q3" s="102" t="s">
         <v>166</v>
@@ -6573,11 +6566,8 @@
       <c r="AR3" s="102" t="s">
         <v>193</v>
       </c>
-      <c r="AS3" s="102" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A4" s="98" t="s">
         <v>154</v>
       </c>
@@ -6585,7 +6575,7 @@
       <c r="C4" s="98"/>
       <c r="D4" s="98"/>
       <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
+      <c r="F4" s="99"/>
       <c r="G4" s="99"/>
       <c r="H4" s="99"/>
       <c r="I4" s="99"/>
@@ -6594,8 +6584,8 @@
       <c r="L4" s="99"/>
       <c r="M4" s="99"/>
       <c r="N4" s="99"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="101"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="103"/>
       <c r="Q4" s="103"/>
       <c r="R4" s="103"/>
       <c r="S4" s="103"/>
@@ -6624,7 +6614,6 @@
       <c r="AP4" s="103"/>
       <c r="AQ4" s="103"/>
       <c r="AR4" s="103"/>
-      <c r="AS4" s="103"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
